--- a/results/power/power_results_by_hierarchy.xlsx
+++ b/results/power/power_results_by_hierarchy.xlsx
@@ -8,14 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev\riscv-power-aware\results\power\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{464105DF-2152-43BC-9BF0-8A3D267133B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07192F74-FEE2-423D-9EC3-5353FABDE7A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{71665766-232F-42B5-8C54-1F711CA08D87}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{71665766-232F-42B5-8C54-1F711CA08D87}"/>
   </bookViews>
   <sheets>
     <sheet name="power_spin" sheetId="1" r:id="rId1"/>
     <sheet name="power_alu" sheetId="2" r:id="rId2"/>
     <sheet name="power_mem" sheetId="3" r:id="rId3"/>
+    <sheet name="power_branch" sheetId="4" r:id="rId4"/>
+    <sheet name="power_chase" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="681" uniqueCount="192">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1135" uniqueCount="192">
   <si>
     <t>Global Resources</t>
   </si>
@@ -707,7 +709,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="3">
+  <dxfs count="9">
     <dxf>
       <font>
         <b/>
@@ -745,6 +747,82 @@
           <color theme="4" tint="0.39997558519241921"/>
         </top>
       </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="0"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4"/>
+          <bgColor theme="4"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="0"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4"/>
+          <bgColor theme="4"/>
+        </patternFill>
+      </fill>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -788,7 +866,7 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{B15E26C1-E4F4-4784-804C-75044EEC47E0}" name="Table3" displayName="Table3" ref="A1:E76" totalsRowShown="0" headerRowDxfId="0" headerRowBorderDxfId="1" tableBorderDxfId="2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{B15E26C1-E4F4-4784-804C-75044EEC47E0}" name="Table3" displayName="Table3" ref="A1:E76" totalsRowShown="0" headerRowDxfId="8" headerRowBorderDxfId="7" tableBorderDxfId="6">
   <autoFilter ref="A1:E76" xr:uid="{B15E26C1-E4F4-4784-804C-75044EEC47E0}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E76">
     <sortCondition descending="1" ref="B1:B76"/>
@@ -799,6 +877,34 @@
     <tableColumn id="3" xr3:uid="{B363E05E-A591-4722-825D-DF06189F9DF4}" name="Current Level Dynamic On-Chip Power (W)"/>
     <tableColumn id="4" xr3:uid="{E3DFC169-377F-4E92-96BF-7E85B405F942}" name="Full Hierarchy Name"/>
     <tableColumn id="5" xr3:uid="{4BFBB5ED-CF9F-4289-B2D1-A5DE474D6F53}" name="Entity Name"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{6621A618-A607-45B2-8D2F-D68FB4900DC2}" name="Table4" displayName="Table4" ref="A1:E76" totalsRowShown="0" headerRowDxfId="3" headerRowBorderDxfId="4" tableBorderDxfId="5">
+  <autoFilter ref="A1:E76" xr:uid="{6621A618-A607-45B2-8D2F-D68FB4900DC2}"/>
+  <tableColumns count="5">
+    <tableColumn id="1" xr3:uid="{45346CE6-87DC-4E53-9D5D-79D6CDEE6798}" name="Compilation Hierarchy Node"/>
+    <tableColumn id="2" xr3:uid="{92B9C947-037A-4AB7-8BCD-F0AEA50A1929}" name="Cumulative Dynamic On-Chip Power (W)"/>
+    <tableColumn id="3" xr3:uid="{AE20CBAF-A324-4755-A507-3DC2671D9516}" name="Current Level Dynamic On-Chip Power (W)"/>
+    <tableColumn id="4" xr3:uid="{371800DC-067A-4BAA-99FE-A6D1B76213D3}" name="Full Hierarchy Name"/>
+    <tableColumn id="5" xr3:uid="{DC92EB74-D179-4636-BC18-236265F0F357}" name="Entity Name"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{661AF9EA-031A-48DC-B7AF-72B2D6F955FE}" name="Table5" displayName="Table5" ref="A1:E76" totalsRowShown="0" headerRowDxfId="0" headerRowBorderDxfId="1" tableBorderDxfId="2">
+  <autoFilter ref="A1:E76" xr:uid="{661AF9EA-031A-48DC-B7AF-72B2D6F955FE}"/>
+  <tableColumns count="5">
+    <tableColumn id="1" xr3:uid="{FAFD6D57-E89E-434D-A461-63F04DC7AA96}" name="Compilation Hierarchy Node"/>
+    <tableColumn id="2" xr3:uid="{8B454DF6-1269-4CC1-BCD9-D845C7509202}" name="Cumulative Dynamic On-Chip Power (W)"/>
+    <tableColumn id="3" xr3:uid="{49CBF02C-88E6-49ED-9800-97DE0CCC66EC}" name="Current Level Dynamic On-Chip Power (W)"/>
+    <tableColumn id="4" xr3:uid="{68F0631B-A17A-4CCA-8F48-28DF685777A9}" name="Full Hierarchy Name"/>
+    <tableColumn id="5" xr3:uid="{1C5F9945-1865-4A8A-9FEB-E9D09FE1B421}" name="Entity Name"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -5026,4 +5132,2610 @@
     <tablePart r:id="rId1"/>
   </tableParts>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E9342C08-D979-4FBE-81C9-BC1102F1F095}">
+  <dimension ref="A1:E76"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="28.7109375" customWidth="1"/>
+    <col min="2" max="2" width="39.5703125" customWidth="1"/>
+    <col min="3" max="3" width="41.42578125" customWidth="1"/>
+    <col min="4" max="4" width="85.7109375" customWidth="1"/>
+    <col min="5" max="5" width="57.5703125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>0.33500000000000002</v>
+      </c>
+      <c r="C2">
+        <v>0.27200000000000002</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3">
+        <v>6.4000000000000001E-2</v>
+      </c>
+      <c r="C3">
+        <v>1.0999999999999999E-2</v>
+      </c>
+      <c r="E3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <v>4.5999999999999999E-2</v>
+      </c>
+      <c r="C4">
+        <v>0</v>
+      </c>
+      <c r="D4" t="s">
+        <v>4</v>
+      </c>
+      <c r="E4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5">
+        <v>4.5999999999999999E-2</v>
+      </c>
+      <c r="C5">
+        <v>0</v>
+      </c>
+      <c r="D5" t="s">
+        <v>7</v>
+      </c>
+      <c r="E5" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6">
+        <v>4.5999999999999999E-2</v>
+      </c>
+      <c r="C6">
+        <v>0</v>
+      </c>
+      <c r="D6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E6" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7">
+        <v>4.5999999999999999E-2</v>
+      </c>
+      <c r="C7">
+        <v>0</v>
+      </c>
+      <c r="D7" t="s">
+        <v>12</v>
+      </c>
+      <c r="E7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8">
+        <v>4.5999999999999999E-2</v>
+      </c>
+      <c r="C8">
+        <v>4.5999999999999999E-2</v>
+      </c>
+      <c r="D8" t="s">
+        <v>15</v>
+      </c>
+      <c r="E8" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>17</v>
+      </c>
+      <c r="B9">
+        <v>6.0000000000000001E-3</v>
+      </c>
+      <c r="C9" s="1">
+        <v>6.9700000000000003E-4</v>
+      </c>
+      <c r="D9" t="s">
+        <v>18</v>
+      </c>
+      <c r="E9" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>20</v>
+      </c>
+      <c r="B10">
+        <v>1E-3</v>
+      </c>
+      <c r="C10" s="1">
+        <v>6.7900000000000002E-6</v>
+      </c>
+      <c r="D10" t="s">
+        <v>21</v>
+      </c>
+      <c r="E10" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>23</v>
+      </c>
+      <c r="B11" s="1">
+        <v>8.7699999999999996E-4</v>
+      </c>
+      <c r="C11">
+        <v>0</v>
+      </c>
+      <c r="D11" t="s">
+        <v>24</v>
+      </c>
+      <c r="E11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>26</v>
+      </c>
+      <c r="B12" s="1">
+        <v>8.7699999999999996E-4</v>
+      </c>
+      <c r="C12">
+        <v>0</v>
+      </c>
+      <c r="D12" t="s">
+        <v>27</v>
+      </c>
+      <c r="E12" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>29</v>
+      </c>
+      <c r="B13" s="1">
+        <v>8.7699999999999996E-4</v>
+      </c>
+      <c r="C13">
+        <v>0</v>
+      </c>
+      <c r="D13" t="s">
+        <v>30</v>
+      </c>
+      <c r="E13" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>32</v>
+      </c>
+      <c r="B14" s="1">
+        <v>8.7699999999999996E-4</v>
+      </c>
+      <c r="C14">
+        <v>0</v>
+      </c>
+      <c r="D14" t="s">
+        <v>33</v>
+      </c>
+      <c r="E14" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>35</v>
+      </c>
+      <c r="B15" s="1">
+        <v>8.7699999999999996E-4</v>
+      </c>
+      <c r="C15" s="1">
+        <v>8.52E-4</v>
+      </c>
+      <c r="D15" t="s">
+        <v>36</v>
+      </c>
+      <c r="E15" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>38</v>
+      </c>
+      <c r="B16" s="1">
+        <v>2.55E-5</v>
+      </c>
+      <c r="C16" s="1">
+        <v>2.55E-5</v>
+      </c>
+      <c r="D16" t="s">
+        <v>39</v>
+      </c>
+      <c r="E16" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>41</v>
+      </c>
+      <c r="B17" s="1">
+        <v>6.3299999999999994E-5</v>
+      </c>
+      <c r="C17" s="1">
+        <v>6.3299999999999994E-5</v>
+      </c>
+      <c r="D17" t="s">
+        <v>42</v>
+      </c>
+      <c r="E17" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>50</v>
+      </c>
+      <c r="B18" s="1">
+        <v>5.4799999999999997E-5</v>
+      </c>
+      <c r="C18" s="1">
+        <v>5.4799999999999997E-5</v>
+      </c>
+      <c r="D18" t="s">
+        <v>51</v>
+      </c>
+      <c r="E18" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>44</v>
+      </c>
+      <c r="B19" s="1">
+        <v>3.6600000000000002E-5</v>
+      </c>
+      <c r="C19" s="1">
+        <v>1.9700000000000001E-5</v>
+      </c>
+      <c r="D19" t="s">
+        <v>45</v>
+      </c>
+      <c r="E19" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>47</v>
+      </c>
+      <c r="B20" s="1">
+        <v>1.6900000000000001E-5</v>
+      </c>
+      <c r="C20" s="1">
+        <v>1.6900000000000001E-5</v>
+      </c>
+      <c r="D20" t="s">
+        <v>48</v>
+      </c>
+      <c r="E20" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>53</v>
+      </c>
+      <c r="B21" s="1">
+        <v>3.4199999999999998E-5</v>
+      </c>
+      <c r="C21" s="1">
+        <v>3.4199999999999998E-5</v>
+      </c>
+      <c r="D21" t="s">
+        <v>54</v>
+      </c>
+      <c r="E21" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>59</v>
+      </c>
+      <c r="B22" s="1">
+        <v>8.8799999999999997E-6</v>
+      </c>
+      <c r="C22" s="1">
+        <v>8.8799999999999997E-6</v>
+      </c>
+      <c r="D22" t="s">
+        <v>60</v>
+      </c>
+      <c r="E22" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>56</v>
+      </c>
+      <c r="B23" s="1">
+        <v>2.4200000000000001E-6</v>
+      </c>
+      <c r="C23" s="1">
+        <v>2.4200000000000001E-6</v>
+      </c>
+      <c r="D23" t="s">
+        <v>57</v>
+      </c>
+      <c r="E23" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>61</v>
+      </c>
+      <c r="B24">
+        <v>1E-3</v>
+      </c>
+      <c r="C24" s="1">
+        <v>7.17E-6</v>
+      </c>
+      <c r="D24" t="s">
+        <v>62</v>
+      </c>
+      <c r="E24" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>64</v>
+      </c>
+      <c r="B25">
+        <v>1E-3</v>
+      </c>
+      <c r="C25">
+        <v>1E-3</v>
+      </c>
+      <c r="D25" t="s">
+        <v>65</v>
+      </c>
+      <c r="E25" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>67</v>
+      </c>
+      <c r="B26" s="1">
+        <v>5.8199999999999998E-5</v>
+      </c>
+      <c r="C26" s="1">
+        <v>5.8199999999999998E-5</v>
+      </c>
+      <c r="D26" t="s">
+        <v>68</v>
+      </c>
+      <c r="E26" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>70</v>
+      </c>
+      <c r="B27" s="1">
+        <v>4.6300000000000001E-5</v>
+      </c>
+      <c r="C27" s="1">
+        <v>4.6300000000000001E-5</v>
+      </c>
+      <c r="D27" t="s">
+        <v>71</v>
+      </c>
+      <c r="E27" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>73</v>
+      </c>
+      <c r="B28" s="1">
+        <v>1.01E-5</v>
+      </c>
+      <c r="C28" s="1">
+        <v>1.01E-5</v>
+      </c>
+      <c r="D28" t="s">
+        <v>74</v>
+      </c>
+      <c r="E28" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>76</v>
+      </c>
+      <c r="B29" s="1">
+        <v>4.8099999999999997E-6</v>
+      </c>
+      <c r="C29" s="1">
+        <v>4.8099999999999997E-6</v>
+      </c>
+      <c r="D29" t="s">
+        <v>77</v>
+      </c>
+      <c r="E29" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>79</v>
+      </c>
+      <c r="B30" s="1">
+        <v>4.3000000000000003E-6</v>
+      </c>
+      <c r="C30" s="1">
+        <v>4.3000000000000003E-6</v>
+      </c>
+      <c r="D30" t="s">
+        <v>80</v>
+      </c>
+      <c r="E30" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>87</v>
+      </c>
+      <c r="B31" s="1">
+        <v>9.1600000000000004E-4</v>
+      </c>
+      <c r="C31" s="1">
+        <v>9.7299999999999993E-5</v>
+      </c>
+      <c r="D31" t="s">
+        <v>88</v>
+      </c>
+      <c r="E31" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>90</v>
+      </c>
+      <c r="B32" s="1">
+        <v>7.6800000000000002E-4</v>
+      </c>
+      <c r="C32" s="1">
+        <v>7.6800000000000002E-4</v>
+      </c>
+      <c r="D32" t="s">
+        <v>91</v>
+      </c>
+      <c r="E32" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>93</v>
+      </c>
+      <c r="B33" s="1">
+        <v>4.9700000000000002E-5</v>
+      </c>
+      <c r="C33" s="1">
+        <v>4.9700000000000002E-5</v>
+      </c>
+      <c r="D33" t="s">
+        <v>94</v>
+      </c>
+      <c r="E33" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>82</v>
+      </c>
+      <c r="B34" s="1">
+        <v>8.6399999999999997E-4</v>
+      </c>
+      <c r="C34" s="1">
+        <v>8.6399999999999997E-4</v>
+      </c>
+      <c r="D34" t="s">
+        <v>83</v>
+      </c>
+      <c r="E34" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>96</v>
+      </c>
+      <c r="B35" s="1">
+        <v>6.3100000000000005E-4</v>
+      </c>
+      <c r="C35" s="1">
+        <v>6.3100000000000005E-4</v>
+      </c>
+      <c r="D35" t="s">
+        <v>97</v>
+      </c>
+      <c r="E35" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>85</v>
+      </c>
+      <c r="B36" s="1">
+        <v>3.3399999999999999E-4</v>
+      </c>
+      <c r="C36" s="1">
+        <v>3.3399999999999999E-4</v>
+      </c>
+      <c r="D36" t="s">
+        <v>86</v>
+      </c>
+      <c r="E36" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>98</v>
+      </c>
+      <c r="B37" s="1">
+        <v>1.11E-4</v>
+      </c>
+      <c r="C37" s="1">
+        <v>1.11E-4</v>
+      </c>
+      <c r="D37" t="s">
+        <v>99</v>
+      </c>
+      <c r="E37" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>115</v>
+      </c>
+      <c r="B38" s="1">
+        <v>1.06E-4</v>
+      </c>
+      <c r="C38" s="1">
+        <v>1.06E-4</v>
+      </c>
+      <c r="D38" t="s">
+        <v>116</v>
+      </c>
+      <c r="E38" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>128</v>
+      </c>
+      <c r="B39" s="1">
+        <v>8.7700000000000004E-5</v>
+      </c>
+      <c r="C39" s="1">
+        <v>8.7700000000000004E-5</v>
+      </c>
+      <c r="D39" t="s">
+        <v>129</v>
+      </c>
+      <c r="E39" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>117</v>
+      </c>
+      <c r="B40" s="1">
+        <v>8.7499999999999999E-5</v>
+      </c>
+      <c r="C40" s="1">
+        <v>8.7499999999999999E-5</v>
+      </c>
+      <c r="D40" t="s">
+        <v>118</v>
+      </c>
+      <c r="E40" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>101</v>
+      </c>
+      <c r="B41" s="1">
+        <v>3.5800000000000003E-5</v>
+      </c>
+      <c r="C41" s="1">
+        <v>3.5800000000000003E-5</v>
+      </c>
+      <c r="D41" t="s">
+        <v>102</v>
+      </c>
+      <c r="E41" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>105</v>
+      </c>
+      <c r="B42" s="1">
+        <v>3.4499999999999998E-5</v>
+      </c>
+      <c r="C42" s="1">
+        <v>3.4499999999999998E-5</v>
+      </c>
+      <c r="D42" t="s">
+        <v>106</v>
+      </c>
+      <c r="E42" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>109</v>
+      </c>
+      <c r="B43" s="1">
+        <v>3.1199999999999999E-5</v>
+      </c>
+      <c r="C43" s="1">
+        <v>3.1199999999999999E-5</v>
+      </c>
+      <c r="D43" t="s">
+        <v>110</v>
+      </c>
+      <c r="E43" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>121</v>
+      </c>
+      <c r="B44" s="1">
+        <v>2.5999999999999998E-5</v>
+      </c>
+      <c r="C44" s="1">
+        <v>2.5999999999999998E-5</v>
+      </c>
+      <c r="D44" t="s">
+        <v>122</v>
+      </c>
+      <c r="E44" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>103</v>
+      </c>
+      <c r="B45" s="1">
+        <v>2.23E-5</v>
+      </c>
+      <c r="C45" s="1">
+        <v>2.23E-5</v>
+      </c>
+      <c r="D45" t="s">
+        <v>104</v>
+      </c>
+      <c r="E45" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>107</v>
+      </c>
+      <c r="B46" s="1">
+        <v>1.9400000000000001E-5</v>
+      </c>
+      <c r="C46" s="1">
+        <v>1.9400000000000001E-5</v>
+      </c>
+      <c r="D46" t="s">
+        <v>108</v>
+      </c>
+      <c r="E46" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>111</v>
+      </c>
+      <c r="B47" s="1">
+        <v>1.7399999999999999E-5</v>
+      </c>
+      <c r="C47" s="1">
+        <v>1.7399999999999999E-5</v>
+      </c>
+      <c r="D47" t="s">
+        <v>112</v>
+      </c>
+      <c r="E47" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>113</v>
+      </c>
+      <c r="B48" s="1">
+        <v>1.7200000000000001E-5</v>
+      </c>
+      <c r="C48" s="1">
+        <v>1.7200000000000001E-5</v>
+      </c>
+      <c r="D48" t="s">
+        <v>114</v>
+      </c>
+      <c r="E48" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>130</v>
+      </c>
+      <c r="B49" s="1">
+        <v>1.5500000000000001E-5</v>
+      </c>
+      <c r="C49" s="1">
+        <v>1.5500000000000001E-5</v>
+      </c>
+      <c r="D49" t="s">
+        <v>131</v>
+      </c>
+      <c r="E49" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>132</v>
+      </c>
+      <c r="B50" s="1">
+        <v>1.19E-5</v>
+      </c>
+      <c r="C50" s="1">
+        <v>1.19E-5</v>
+      </c>
+      <c r="D50" t="s">
+        <v>133</v>
+      </c>
+      <c r="E50" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>119</v>
+      </c>
+      <c r="B51" s="1">
+        <v>9.4099999999999997E-6</v>
+      </c>
+      <c r="C51" s="1">
+        <v>9.4099999999999997E-6</v>
+      </c>
+      <c r="D51" t="s">
+        <v>120</v>
+      </c>
+      <c r="E51" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>126</v>
+      </c>
+      <c r="B52" s="1">
+        <v>9.1800000000000002E-6</v>
+      </c>
+      <c r="C52" s="1">
+        <v>9.1800000000000002E-6</v>
+      </c>
+      <c r="D52" t="s">
+        <v>127</v>
+      </c>
+      <c r="E52" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>123</v>
+      </c>
+      <c r="B53" s="1">
+        <v>4.0500000000000002E-6</v>
+      </c>
+      <c r="C53" s="1">
+        <v>4.0500000000000002E-6</v>
+      </c>
+      <c r="D53" t="s">
+        <v>124</v>
+      </c>
+      <c r="E53" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>134</v>
+      </c>
+      <c r="B54" s="1">
+        <v>2.7199999999999998E-6</v>
+      </c>
+      <c r="C54" s="1">
+        <v>2.7199999999999998E-6</v>
+      </c>
+      <c r="D54" t="s">
+        <v>135</v>
+      </c>
+      <c r="E54" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>136</v>
+      </c>
+      <c r="B55" s="1">
+        <v>2.5900000000000002E-6</v>
+      </c>
+      <c r="C55" s="1">
+        <v>2.5900000000000002E-6</v>
+      </c>
+      <c r="D55" t="s">
+        <v>137</v>
+      </c>
+      <c r="E55" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>138</v>
+      </c>
+      <c r="B56" s="1">
+        <v>1.9199999999999998E-6</v>
+      </c>
+      <c r="C56" s="1">
+        <v>1.9199999999999998E-6</v>
+      </c>
+      <c r="D56" t="s">
+        <v>139</v>
+      </c>
+      <c r="E56" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>140</v>
+      </c>
+      <c r="B57" s="1">
+        <v>8.8700000000000004E-7</v>
+      </c>
+      <c r="C57" s="1">
+        <v>8.8700000000000004E-7</v>
+      </c>
+      <c r="D57" t="s">
+        <v>141</v>
+      </c>
+      <c r="E57" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>142</v>
+      </c>
+      <c r="B58" s="1">
+        <v>5.7800000000000001E-7</v>
+      </c>
+      <c r="C58" s="1">
+        <v>5.7800000000000001E-7</v>
+      </c>
+      <c r="D58" t="s">
+        <v>143</v>
+      </c>
+      <c r="E58" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>146</v>
+      </c>
+      <c r="B59" s="1">
+        <v>5.2600000000000002E-7</v>
+      </c>
+      <c r="C59" s="1">
+        <v>5.2600000000000002E-7</v>
+      </c>
+      <c r="D59" t="s">
+        <v>147</v>
+      </c>
+      <c r="E59" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>148</v>
+      </c>
+      <c r="B60" s="1">
+        <v>5.2600000000000002E-7</v>
+      </c>
+      <c r="C60" s="1">
+        <v>5.2600000000000002E-7</v>
+      </c>
+      <c r="D60" t="s">
+        <v>149</v>
+      </c>
+      <c r="E60" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>150</v>
+      </c>
+      <c r="B61" s="1">
+        <v>5.2600000000000002E-7</v>
+      </c>
+      <c r="C61" s="1">
+        <v>5.2600000000000002E-7</v>
+      </c>
+      <c r="D61" t="s">
+        <v>151</v>
+      </c>
+      <c r="E61" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>144</v>
+      </c>
+      <c r="B62" s="1">
+        <v>4.6899999999999998E-7</v>
+      </c>
+      <c r="C62" s="1">
+        <v>4.6899999999999998E-7</v>
+      </c>
+      <c r="D62" t="s">
+        <v>145</v>
+      </c>
+      <c r="E62" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>152</v>
+      </c>
+      <c r="B63" s="1">
+        <v>2.9999999999999999E-7</v>
+      </c>
+      <c r="C63" s="1">
+        <v>2.9999999999999999E-7</v>
+      </c>
+      <c r="D63" t="s">
+        <v>153</v>
+      </c>
+      <c r="E63" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>154</v>
+      </c>
+      <c r="B64" s="1">
+        <v>2.96E-7</v>
+      </c>
+      <c r="C64" s="1">
+        <v>2.96E-7</v>
+      </c>
+      <c r="D64" t="s">
+        <v>155</v>
+      </c>
+      <c r="E64" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>156</v>
+      </c>
+      <c r="B65" s="1">
+        <v>5.7200000000000003E-4</v>
+      </c>
+      <c r="C65">
+        <v>0</v>
+      </c>
+      <c r="D65" t="s">
+        <v>157</v>
+      </c>
+      <c r="E65" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>159</v>
+      </c>
+      <c r="B66" s="1">
+        <v>5.7200000000000003E-4</v>
+      </c>
+      <c r="C66">
+        <v>0</v>
+      </c>
+      <c r="D66" t="s">
+        <v>160</v>
+      </c>
+      <c r="E66" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>32</v>
+      </c>
+      <c r="B67" s="1">
+        <v>5.7200000000000003E-4</v>
+      </c>
+      <c r="C67">
+        <v>0</v>
+      </c>
+      <c r="D67" t="s">
+        <v>161</v>
+      </c>
+      <c r="E67" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>35</v>
+      </c>
+      <c r="B68" s="1">
+        <v>5.7200000000000003E-4</v>
+      </c>
+      <c r="C68" s="1">
+        <v>5.7200000000000003E-4</v>
+      </c>
+      <c r="D68" t="s">
+        <v>163</v>
+      </c>
+      <c r="E68" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>165</v>
+      </c>
+      <c r="B69" s="1">
+        <v>3.8700000000000001E-7</v>
+      </c>
+      <c r="C69" s="1">
+        <v>3.8700000000000001E-7</v>
+      </c>
+      <c r="D69" t="s">
+        <v>166</v>
+      </c>
+      <c r="E69" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>38</v>
+      </c>
+      <c r="B70" s="1">
+        <v>5.1399999999999998E-10</v>
+      </c>
+      <c r="C70" s="1">
+        <v>5.1399999999999998E-10</v>
+      </c>
+      <c r="D70" t="s">
+        <v>168</v>
+      </c>
+      <c r="E70" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>169</v>
+      </c>
+      <c r="B71" s="1">
+        <v>1.15E-4</v>
+      </c>
+      <c r="C71" s="1">
+        <v>1.15E-4</v>
+      </c>
+      <c r="D71" t="s">
+        <v>170</v>
+      </c>
+      <c r="E71" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>172</v>
+      </c>
+      <c r="B72" s="1">
+        <v>2.0699999999999998E-5</v>
+      </c>
+      <c r="C72" s="1">
+        <v>2.0699999999999998E-5</v>
+      </c>
+      <c r="D72" t="s">
+        <v>173</v>
+      </c>
+      <c r="E72" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>175</v>
+      </c>
+      <c r="B73" s="1">
+        <v>5.5700000000000002E-7</v>
+      </c>
+      <c r="C73" s="1">
+        <v>5.5700000000000002E-7</v>
+      </c>
+      <c r="D73" t="s">
+        <v>176</v>
+      </c>
+      <c r="E73" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>178</v>
+      </c>
+      <c r="B74">
+        <v>0</v>
+      </c>
+      <c r="C74">
+        <v>0</v>
+      </c>
+      <c r="D74" t="s">
+        <v>179</v>
+      </c>
+      <c r="E74" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>181</v>
+      </c>
+      <c r="B75">
+        <v>0</v>
+      </c>
+      <c r="C75">
+        <v>0</v>
+      </c>
+      <c r="D75" t="s">
+        <v>182</v>
+      </c>
+      <c r="E75" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>184</v>
+      </c>
+      <c r="B76">
+        <v>0</v>
+      </c>
+      <c r="C76">
+        <v>0</v>
+      </c>
+      <c r="D76" t="s">
+        <v>185</v>
+      </c>
+      <c r="E76" t="s">
+        <v>186</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BAE15965-3211-4FBB-8692-E47112645D65}">
+  <dimension ref="A1:E76"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="28.7109375" customWidth="1"/>
+    <col min="2" max="2" width="39.5703125" customWidth="1"/>
+    <col min="3" max="3" width="41.42578125" customWidth="1"/>
+    <col min="4" max="4" width="96.7109375" customWidth="1"/>
+    <col min="5" max="5" width="57.42578125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>0.33400000000000002</v>
+      </c>
+      <c r="C2">
+        <v>0.27200000000000002</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3">
+        <v>6.2E-2</v>
+      </c>
+      <c r="C3">
+        <v>1.0999999999999999E-2</v>
+      </c>
+      <c r="E3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <v>4.5999999999999999E-2</v>
+      </c>
+      <c r="C4">
+        <v>0</v>
+      </c>
+      <c r="D4" t="s">
+        <v>4</v>
+      </c>
+      <c r="E4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5">
+        <v>4.5999999999999999E-2</v>
+      </c>
+      <c r="C5">
+        <v>0</v>
+      </c>
+      <c r="D5" t="s">
+        <v>7</v>
+      </c>
+      <c r="E5" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6">
+        <v>4.5999999999999999E-2</v>
+      </c>
+      <c r="C6">
+        <v>0</v>
+      </c>
+      <c r="D6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E6" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7">
+        <v>4.5999999999999999E-2</v>
+      </c>
+      <c r="C7">
+        <v>0</v>
+      </c>
+      <c r="D7" t="s">
+        <v>12</v>
+      </c>
+      <c r="E7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8">
+        <v>4.5999999999999999E-2</v>
+      </c>
+      <c r="C8">
+        <v>4.5999999999999999E-2</v>
+      </c>
+      <c r="D8" t="s">
+        <v>15</v>
+      </c>
+      <c r="E8" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>17</v>
+      </c>
+      <c r="B9">
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="C9" s="1">
+        <v>4.8299999999999998E-4</v>
+      </c>
+      <c r="D9" t="s">
+        <v>18</v>
+      </c>
+      <c r="E9" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>20</v>
+      </c>
+      <c r="B10" s="1">
+        <v>9.4300000000000004E-4</v>
+      </c>
+      <c r="C10" s="1">
+        <v>2.1999999999999999E-5</v>
+      </c>
+      <c r="D10" t="s">
+        <v>21</v>
+      </c>
+      <c r="E10" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>23</v>
+      </c>
+      <c r="B11" s="1">
+        <v>7.6199999999999998E-4</v>
+      </c>
+      <c r="C11">
+        <v>0</v>
+      </c>
+      <c r="D11" t="s">
+        <v>24</v>
+      </c>
+      <c r="E11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>26</v>
+      </c>
+      <c r="B12" s="1">
+        <v>7.6199999999999998E-4</v>
+      </c>
+      <c r="C12">
+        <v>0</v>
+      </c>
+      <c r="D12" t="s">
+        <v>27</v>
+      </c>
+      <c r="E12" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>29</v>
+      </c>
+      <c r="B13" s="1">
+        <v>7.6199999999999998E-4</v>
+      </c>
+      <c r="C13">
+        <v>0</v>
+      </c>
+      <c r="D13" t="s">
+        <v>30</v>
+      </c>
+      <c r="E13" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>32</v>
+      </c>
+      <c r="B14" s="1">
+        <v>7.6199999999999998E-4</v>
+      </c>
+      <c r="C14">
+        <v>0</v>
+      </c>
+      <c r="D14" t="s">
+        <v>33</v>
+      </c>
+      <c r="E14" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>35</v>
+      </c>
+      <c r="B15" s="1">
+        <v>7.6199999999999998E-4</v>
+      </c>
+      <c r="C15" s="1">
+        <v>7.4399999999999998E-4</v>
+      </c>
+      <c r="D15" t="s">
+        <v>36</v>
+      </c>
+      <c r="E15" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>38</v>
+      </c>
+      <c r="B16" s="1">
+        <v>1.7799999999999999E-5</v>
+      </c>
+      <c r="C16" s="1">
+        <v>1.7799999999999999E-5</v>
+      </c>
+      <c r="D16" t="s">
+        <v>39</v>
+      </c>
+      <c r="E16" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>41</v>
+      </c>
+      <c r="B17" s="1">
+        <v>6.2799999999999995E-5</v>
+      </c>
+      <c r="C17" s="1">
+        <v>6.2799999999999995E-5</v>
+      </c>
+      <c r="D17" t="s">
+        <v>42</v>
+      </c>
+      <c r="E17" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>50</v>
+      </c>
+      <c r="B18" s="1">
+        <v>3.2499999999999997E-5</v>
+      </c>
+      <c r="C18" s="1">
+        <v>3.2499999999999997E-5</v>
+      </c>
+      <c r="D18" t="s">
+        <v>51</v>
+      </c>
+      <c r="E18" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>44</v>
+      </c>
+      <c r="B19" s="1">
+        <v>2.8200000000000001E-5</v>
+      </c>
+      <c r="C19" s="1">
+        <v>1.4800000000000001E-5</v>
+      </c>
+      <c r="D19" t="s">
+        <v>45</v>
+      </c>
+      <c r="E19" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>47</v>
+      </c>
+      <c r="B20" s="1">
+        <v>1.34E-5</v>
+      </c>
+      <c r="C20" s="1">
+        <v>1.34E-5</v>
+      </c>
+      <c r="D20" t="s">
+        <v>48</v>
+      </c>
+      <c r="E20" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>53</v>
+      </c>
+      <c r="B21" s="1">
+        <v>2.6100000000000001E-5</v>
+      </c>
+      <c r="C21" s="1">
+        <v>2.6100000000000001E-5</v>
+      </c>
+      <c r="D21" t="s">
+        <v>54</v>
+      </c>
+      <c r="E21" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>59</v>
+      </c>
+      <c r="B22" s="1">
+        <v>5.4500000000000003E-6</v>
+      </c>
+      <c r="C22" s="1">
+        <v>5.4500000000000003E-6</v>
+      </c>
+      <c r="D22" t="s">
+        <v>60</v>
+      </c>
+      <c r="E22" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>56</v>
+      </c>
+      <c r="B23" s="1">
+        <v>4.0899999999999998E-6</v>
+      </c>
+      <c r="C23" s="1">
+        <v>4.0899999999999998E-6</v>
+      </c>
+      <c r="D23" t="s">
+        <v>57</v>
+      </c>
+      <c r="E23" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>61</v>
+      </c>
+      <c r="B24" s="1">
+        <v>8.6799999999999996E-4</v>
+      </c>
+      <c r="C24" s="1">
+        <v>5.2599999999999996E-6</v>
+      </c>
+      <c r="D24" t="s">
+        <v>62</v>
+      </c>
+      <c r="E24" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>64</v>
+      </c>
+      <c r="B25" s="1">
+        <v>7.3899999999999997E-4</v>
+      </c>
+      <c r="C25" s="1">
+        <v>7.3899999999999997E-4</v>
+      </c>
+      <c r="D25" t="s">
+        <v>65</v>
+      </c>
+      <c r="E25" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>70</v>
+      </c>
+      <c r="B26" s="1">
+        <v>7.6500000000000003E-5</v>
+      </c>
+      <c r="C26" s="1">
+        <v>7.6500000000000003E-5</v>
+      </c>
+      <c r="D26" t="s">
+        <v>71</v>
+      </c>
+      <c r="E26" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>67</v>
+      </c>
+      <c r="B27" s="1">
+        <v>3.1900000000000003E-5</v>
+      </c>
+      <c r="C27" s="1">
+        <v>3.1900000000000003E-5</v>
+      </c>
+      <c r="D27" t="s">
+        <v>68</v>
+      </c>
+      <c r="E27" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>79</v>
+      </c>
+      <c r="B28" s="1">
+        <v>9.0000000000000002E-6</v>
+      </c>
+      <c r="C28" s="1">
+        <v>9.0000000000000002E-6</v>
+      </c>
+      <c r="D28" t="s">
+        <v>80</v>
+      </c>
+      <c r="E28" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>73</v>
+      </c>
+      <c r="B29" s="1">
+        <v>4.7199999999999997E-6</v>
+      </c>
+      <c r="C29" s="1">
+        <v>4.7199999999999997E-6</v>
+      </c>
+      <c r="D29" t="s">
+        <v>74</v>
+      </c>
+      <c r="E29" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>76</v>
+      </c>
+      <c r="B30" s="1">
+        <v>2.3800000000000001E-6</v>
+      </c>
+      <c r="C30" s="1">
+        <v>2.3800000000000001E-6</v>
+      </c>
+      <c r="D30" t="s">
+        <v>77</v>
+      </c>
+      <c r="E30" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>87</v>
+      </c>
+      <c r="B31" s="1">
+        <v>6.5700000000000003E-4</v>
+      </c>
+      <c r="C31" s="1">
+        <v>1.02E-4</v>
+      </c>
+      <c r="D31" t="s">
+        <v>88</v>
+      </c>
+      <c r="E31" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>90</v>
+      </c>
+      <c r="B32" s="1">
+        <v>5.1099999999999995E-4</v>
+      </c>
+      <c r="C32" s="1">
+        <v>5.1099999999999995E-4</v>
+      </c>
+      <c r="D32" t="s">
+        <v>91</v>
+      </c>
+      <c r="E32" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>93</v>
+      </c>
+      <c r="B33" s="1">
+        <v>4.3800000000000001E-5</v>
+      </c>
+      <c r="C33" s="1">
+        <v>4.3800000000000001E-5</v>
+      </c>
+      <c r="D33" t="s">
+        <v>94</v>
+      </c>
+      <c r="E33" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>82</v>
+      </c>
+      <c r="B34" s="1">
+        <v>3.9300000000000001E-4</v>
+      </c>
+      <c r="C34" s="1">
+        <v>3.9300000000000001E-4</v>
+      </c>
+      <c r="D34" t="s">
+        <v>83</v>
+      </c>
+      <c r="E34" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>96</v>
+      </c>
+      <c r="B35" s="1">
+        <v>3.8400000000000001E-4</v>
+      </c>
+      <c r="C35" s="1">
+        <v>3.8400000000000001E-4</v>
+      </c>
+      <c r="D35" t="s">
+        <v>97</v>
+      </c>
+      <c r="E35" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>85</v>
+      </c>
+      <c r="B36" s="1">
+        <v>2.0699999999999999E-4</v>
+      </c>
+      <c r="C36" s="1">
+        <v>2.0699999999999999E-4</v>
+      </c>
+      <c r="D36" t="s">
+        <v>86</v>
+      </c>
+      <c r="E36" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>98</v>
+      </c>
+      <c r="B37" s="1">
+        <v>1.92E-4</v>
+      </c>
+      <c r="C37" s="1">
+        <v>1.92E-4</v>
+      </c>
+      <c r="D37" t="s">
+        <v>99</v>
+      </c>
+      <c r="E37" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>115</v>
+      </c>
+      <c r="B38" s="1">
+        <v>8.5599999999999994E-5</v>
+      </c>
+      <c r="C38" s="1">
+        <v>8.5599999999999994E-5</v>
+      </c>
+      <c r="D38" t="s">
+        <v>116</v>
+      </c>
+      <c r="E38" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>117</v>
+      </c>
+      <c r="B39" s="1">
+        <v>7.8100000000000001E-5</v>
+      </c>
+      <c r="C39" s="1">
+        <v>7.8100000000000001E-5</v>
+      </c>
+      <c r="D39" t="s">
+        <v>118</v>
+      </c>
+      <c r="E39" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>101</v>
+      </c>
+      <c r="B40" s="1">
+        <v>4.2799999999999997E-5</v>
+      </c>
+      <c r="C40" s="1">
+        <v>4.2799999999999997E-5</v>
+      </c>
+      <c r="D40" t="s">
+        <v>102</v>
+      </c>
+      <c r="E40" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>105</v>
+      </c>
+      <c r="B41" s="1">
+        <v>3.9799999999999998E-5</v>
+      </c>
+      <c r="C41" s="1">
+        <v>3.9799999999999998E-5</v>
+      </c>
+      <c r="D41" t="s">
+        <v>106</v>
+      </c>
+      <c r="E41" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>103</v>
+      </c>
+      <c r="B42" s="1">
+        <v>3.96E-5</v>
+      </c>
+      <c r="C42" s="1">
+        <v>3.96E-5</v>
+      </c>
+      <c r="D42" t="s">
+        <v>104</v>
+      </c>
+      <c r="E42" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>111</v>
+      </c>
+      <c r="B43" s="1">
+        <v>3.1199999999999999E-5</v>
+      </c>
+      <c r="C43" s="1">
+        <v>3.1199999999999999E-5</v>
+      </c>
+      <c r="D43" t="s">
+        <v>112</v>
+      </c>
+      <c r="E43" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>113</v>
+      </c>
+      <c r="B44" s="1">
+        <v>2.9899999999999998E-5</v>
+      </c>
+      <c r="C44" s="1">
+        <v>2.9899999999999998E-5</v>
+      </c>
+      <c r="D44" t="s">
+        <v>114</v>
+      </c>
+      <c r="E44" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>148</v>
+      </c>
+      <c r="B45" s="1">
+        <v>2.9499999999999999E-5</v>
+      </c>
+      <c r="C45" s="1">
+        <v>2.9499999999999999E-5</v>
+      </c>
+      <c r="D45" t="s">
+        <v>149</v>
+      </c>
+      <c r="E45" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>150</v>
+      </c>
+      <c r="B46" s="1">
+        <v>2.55E-5</v>
+      </c>
+      <c r="C46" s="1">
+        <v>2.55E-5</v>
+      </c>
+      <c r="D46" t="s">
+        <v>151</v>
+      </c>
+      <c r="E46" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>109</v>
+      </c>
+      <c r="B47" s="1">
+        <v>2.4600000000000002E-5</v>
+      </c>
+      <c r="C47" s="1">
+        <v>2.4600000000000002E-5</v>
+      </c>
+      <c r="D47" t="s">
+        <v>110</v>
+      </c>
+      <c r="E47" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>107</v>
+      </c>
+      <c r="B48" s="1">
+        <v>2.4199999999999999E-5</v>
+      </c>
+      <c r="C48" s="1">
+        <v>2.4199999999999999E-5</v>
+      </c>
+      <c r="D48" t="s">
+        <v>108</v>
+      </c>
+      <c r="E48" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>126</v>
+      </c>
+      <c r="B49" s="1">
+        <v>2.34E-5</v>
+      </c>
+      <c r="C49" s="1">
+        <v>2.34E-5</v>
+      </c>
+      <c r="D49" t="s">
+        <v>127</v>
+      </c>
+      <c r="E49" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>121</v>
+      </c>
+      <c r="B50" s="1">
+        <v>2.0599999999999999E-5</v>
+      </c>
+      <c r="C50" s="1">
+        <v>2.0599999999999999E-5</v>
+      </c>
+      <c r="D50" t="s">
+        <v>122</v>
+      </c>
+      <c r="E50" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>119</v>
+      </c>
+      <c r="B51" s="1">
+        <v>1.52E-5</v>
+      </c>
+      <c r="C51" s="1">
+        <v>1.52E-5</v>
+      </c>
+      <c r="D51" t="s">
+        <v>120</v>
+      </c>
+      <c r="E51" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>128</v>
+      </c>
+      <c r="B52" s="1">
+        <v>1.27E-5</v>
+      </c>
+      <c r="C52" s="1">
+        <v>1.27E-5</v>
+      </c>
+      <c r="D52" t="s">
+        <v>129</v>
+      </c>
+      <c r="E52" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>132</v>
+      </c>
+      <c r="B53" s="1">
+        <v>1.2300000000000001E-5</v>
+      </c>
+      <c r="C53" s="1">
+        <v>1.2300000000000001E-5</v>
+      </c>
+      <c r="D53" t="s">
+        <v>133</v>
+      </c>
+      <c r="E53" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>130</v>
+      </c>
+      <c r="B54" s="1">
+        <v>1.1199999999999999E-5</v>
+      </c>
+      <c r="C54" s="1">
+        <v>1.1199999999999999E-5</v>
+      </c>
+      <c r="D54" t="s">
+        <v>131</v>
+      </c>
+      <c r="E54" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>154</v>
+      </c>
+      <c r="B55" s="1">
+        <v>9.2199999999999998E-6</v>
+      </c>
+      <c r="C55" s="1">
+        <v>9.2199999999999998E-6</v>
+      </c>
+      <c r="D55" t="s">
+        <v>155</v>
+      </c>
+      <c r="E55" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>134</v>
+      </c>
+      <c r="B56" s="1">
+        <v>6.3400000000000003E-6</v>
+      </c>
+      <c r="C56" s="1">
+        <v>6.3400000000000003E-6</v>
+      </c>
+      <c r="D56" t="s">
+        <v>135</v>
+      </c>
+      <c r="E56" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>136</v>
+      </c>
+      <c r="B57" s="1">
+        <v>5.8900000000000004E-6</v>
+      </c>
+      <c r="C57" s="1">
+        <v>5.8900000000000004E-6</v>
+      </c>
+      <c r="D57" t="s">
+        <v>137</v>
+      </c>
+      <c r="E57" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>138</v>
+      </c>
+      <c r="B58" s="1">
+        <v>4.2400000000000001E-6</v>
+      </c>
+      <c r="C58" s="1">
+        <v>4.2400000000000001E-6</v>
+      </c>
+      <c r="D58" t="s">
+        <v>139</v>
+      </c>
+      <c r="E58" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>123</v>
+      </c>
+      <c r="B59" s="1">
+        <v>3.4999999999999999E-6</v>
+      </c>
+      <c r="C59" s="1">
+        <v>3.4999999999999999E-6</v>
+      </c>
+      <c r="D59" t="s">
+        <v>124</v>
+      </c>
+      <c r="E59" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>140</v>
+      </c>
+      <c r="B60" s="1">
+        <v>1.2899999999999999E-6</v>
+      </c>
+      <c r="C60" s="1">
+        <v>1.2899999999999999E-6</v>
+      </c>
+      <c r="D60" t="s">
+        <v>141</v>
+      </c>
+      <c r="E60" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>142</v>
+      </c>
+      <c r="B61" s="1">
+        <v>7.7100000000000001E-7</v>
+      </c>
+      <c r="C61" s="1">
+        <v>7.7100000000000001E-7</v>
+      </c>
+      <c r="D61" t="s">
+        <v>143</v>
+      </c>
+      <c r="E61" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>146</v>
+      </c>
+      <c r="B62" s="1">
+        <v>5.2600000000000002E-7</v>
+      </c>
+      <c r="C62" s="1">
+        <v>5.2600000000000002E-7</v>
+      </c>
+      <c r="D62" t="s">
+        <v>147</v>
+      </c>
+      <c r="E62" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>144</v>
+      </c>
+      <c r="B63" s="1">
+        <v>4.3500000000000002E-7</v>
+      </c>
+      <c r="C63" s="1">
+        <v>4.3500000000000002E-7</v>
+      </c>
+      <c r="D63" t="s">
+        <v>145</v>
+      </c>
+      <c r="E63" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>152</v>
+      </c>
+      <c r="B64" s="1">
+        <v>3.2599999999999998E-7</v>
+      </c>
+      <c r="C64" s="1">
+        <v>3.2599999999999998E-7</v>
+      </c>
+      <c r="D64" t="s">
+        <v>153</v>
+      </c>
+      <c r="E64" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>156</v>
+      </c>
+      <c r="B65" s="1">
+        <v>7.0699999999999995E-4</v>
+      </c>
+      <c r="C65">
+        <v>0</v>
+      </c>
+      <c r="D65" t="s">
+        <v>157</v>
+      </c>
+      <c r="E65" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>159</v>
+      </c>
+      <c r="B66" s="1">
+        <v>7.0699999999999995E-4</v>
+      </c>
+      <c r="C66">
+        <v>0</v>
+      </c>
+      <c r="D66" t="s">
+        <v>160</v>
+      </c>
+      <c r="E66" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>32</v>
+      </c>
+      <c r="B67" s="1">
+        <v>7.0699999999999995E-4</v>
+      </c>
+      <c r="C67">
+        <v>0</v>
+      </c>
+      <c r="D67" t="s">
+        <v>161</v>
+      </c>
+      <c r="E67" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>35</v>
+      </c>
+      <c r="B68" s="1">
+        <v>7.0699999999999995E-4</v>
+      </c>
+      <c r="C68" s="1">
+        <v>7.0200000000000004E-4</v>
+      </c>
+      <c r="D68" t="s">
+        <v>163</v>
+      </c>
+      <c r="E68" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>38</v>
+      </c>
+      <c r="B69" s="1">
+        <v>4.6199999999999998E-6</v>
+      </c>
+      <c r="C69" s="1">
+        <v>4.6199999999999998E-6</v>
+      </c>
+      <c r="D69" t="s">
+        <v>168</v>
+      </c>
+      <c r="E69" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>165</v>
+      </c>
+      <c r="B70" s="1">
+        <v>1.37E-7</v>
+      </c>
+      <c r="C70" s="1">
+        <v>1.37E-7</v>
+      </c>
+      <c r="D70" t="s">
+        <v>166</v>
+      </c>
+      <c r="E70" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>169</v>
+      </c>
+      <c r="B71" s="1">
+        <v>1.37E-4</v>
+      </c>
+      <c r="C71" s="1">
+        <v>1.37E-4</v>
+      </c>
+      <c r="D71" t="s">
+        <v>170</v>
+      </c>
+      <c r="E71" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>172</v>
+      </c>
+      <c r="B72" s="1">
+        <v>2.62E-5</v>
+      </c>
+      <c r="C72" s="1">
+        <v>2.62E-5</v>
+      </c>
+      <c r="D72" t="s">
+        <v>173</v>
+      </c>
+      <c r="E72" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>175</v>
+      </c>
+      <c r="B73" s="1">
+        <v>5.5700000000000002E-7</v>
+      </c>
+      <c r="C73" s="1">
+        <v>5.5700000000000002E-7</v>
+      </c>
+      <c r="D73" t="s">
+        <v>176</v>
+      </c>
+      <c r="E73" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>178</v>
+      </c>
+      <c r="B74">
+        <v>0</v>
+      </c>
+      <c r="C74">
+        <v>0</v>
+      </c>
+      <c r="D74" t="s">
+        <v>179</v>
+      </c>
+      <c r="E74" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>181</v>
+      </c>
+      <c r="B75">
+        <v>0</v>
+      </c>
+      <c r="C75">
+        <v>0</v>
+      </c>
+      <c r="D75" t="s">
+        <v>182</v>
+      </c>
+      <c r="E75" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>184</v>
+      </c>
+      <c r="B76">
+        <v>0</v>
+      </c>
+      <c r="C76">
+        <v>0</v>
+      </c>
+      <c r="D76" t="s">
+        <v>185</v>
+      </c>
+      <c r="E76" t="s">
+        <v>186</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
 </file>
--- a/results/power/power_results_by_hierarchy.xlsx
+++ b/results/power/power_results_by_hierarchy.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev\riscv-power-aware\results\power\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07192F74-FEE2-423D-9EC3-5353FABDE7A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2CDEEEC-9846-4ABC-8E5F-205A3CE570F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{71665766-232F-42B5-8C54-1F711CA08D87}"/>
   </bookViews>

--- a/results/power/power_results_by_hierarchy.xlsx
+++ b/results/power/power_results_by_hierarchy.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev\riscv-power-aware\results\power\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2CDEEEC-9846-4ABC-8E5F-205A3CE570F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA583608-300B-4BB5-90E8-246587E5648C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{71665766-232F-42B5-8C54-1F711CA08D87}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{71665766-232F-42B5-8C54-1F711CA08D87}"/>
   </bookViews>
   <sheets>
     <sheet name="power_spin" sheetId="1" r:id="rId1"/>
@@ -711,41 +711,17 @@
   </cellStyles>
   <dxfs count="9">
     <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="0"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4"/>
-          <bgColor theme="4"/>
-        </patternFill>
-      </fill>
+      <border outline="0">
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+      </border>
     </dxf>
     <dxf>
       <border outline="0">
         <bottom style="thin">
           <color theme="4" tint="0.39997558519241921"/>
         </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
       </border>
     </dxf>
     <dxf>
@@ -774,17 +750,41 @@
     </dxf>
     <dxf>
       <border outline="0">
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
         <bottom style="thin">
           <color theme="4" tint="0.39997558519241921"/>
         </bottom>
       </border>
     </dxf>
     <dxf>
-      <border outline="0">
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-      </border>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="0"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4"/>
+          <bgColor theme="4"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <border outline="0">
@@ -854,6 +854,9 @@
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{7BC193C3-1E6C-4B35-8AA7-84A1FC9F1A9B}" name="Table2" displayName="Table2" ref="A1:E76" totalsRowShown="0">
   <autoFilter ref="A1:E76" xr:uid="{7BC193C3-1E6C-4B35-8AA7-84A1FC9F1A9B}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E76">
+    <sortCondition descending="1" ref="B1:B76"/>
+  </sortState>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{D3EEA8F7-7C1D-4291-BEE9-D527C6E1A046}" name="Compilation Hierarchy Node"/>
     <tableColumn id="2" xr3:uid="{6F738B05-BA3E-4247-A350-FC7FD40ECF23}" name="Cumulative Dynamic On-Chip Power (W)"/>
@@ -866,7 +869,7 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{B15E26C1-E4F4-4784-804C-75044EEC47E0}" name="Table3" displayName="Table3" ref="A1:E76" totalsRowShown="0" headerRowDxfId="8" headerRowBorderDxfId="7" tableBorderDxfId="6">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{B15E26C1-E4F4-4784-804C-75044EEC47E0}" name="Table3" displayName="Table3" ref="A1:E76" totalsRowShown="0" headerRowDxfId="5" headerRowBorderDxfId="4" tableBorderDxfId="3">
   <autoFilter ref="A1:E76" xr:uid="{B15E26C1-E4F4-4784-804C-75044EEC47E0}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E76">
     <sortCondition descending="1" ref="B1:B76"/>
@@ -883,8 +886,11 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{6621A618-A607-45B2-8D2F-D68FB4900DC2}" name="Table4" displayName="Table4" ref="A1:E76" totalsRowShown="0" headerRowDxfId="3" headerRowBorderDxfId="4" tableBorderDxfId="5">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{6621A618-A607-45B2-8D2F-D68FB4900DC2}" name="Table4" displayName="Table4" ref="A1:E76" totalsRowShown="0" headerRowDxfId="2" headerRowBorderDxfId="1" tableBorderDxfId="0">
   <autoFilter ref="A1:E76" xr:uid="{6621A618-A607-45B2-8D2F-D68FB4900DC2}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E76">
+    <sortCondition descending="1" ref="B1:B76"/>
+  </sortState>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{45346CE6-87DC-4E53-9D5D-79D6CDEE6798}" name="Compilation Hierarchy Node"/>
     <tableColumn id="2" xr3:uid="{92B9C947-037A-4AB7-8BCD-F0AEA50A1929}" name="Cumulative Dynamic On-Chip Power (W)"/>
@@ -897,8 +903,11 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{661AF9EA-031A-48DC-B7AF-72B2D6F955FE}" name="Table5" displayName="Table5" ref="A1:E76" totalsRowShown="0" headerRowDxfId="0" headerRowBorderDxfId="1" tableBorderDxfId="2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{661AF9EA-031A-48DC-B7AF-72B2D6F955FE}" name="Table5" displayName="Table5" ref="A1:E76" totalsRowShown="0" headerRowDxfId="8" headerRowBorderDxfId="7" tableBorderDxfId="6">
   <autoFilter ref="A1:E76" xr:uid="{661AF9EA-031A-48DC-B7AF-72B2D6F955FE}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E76">
+    <sortCondition descending="1" ref="B1:B76"/>
+  </sortState>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{FAFD6D57-E89E-434D-A461-63F04DC7AA96}" name="Compilation Hierarchy Node"/>
     <tableColumn id="2" xr3:uid="{8B454DF6-1269-4CC1-BCD9-D845C7509202}" name="Cumulative Dynamic On-Chip Power (W)"/>
@@ -1228,16 +1237,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{914A8387-7BCF-4A51-982E-D899702FCAD3}">
   <dimension ref="A1:E76"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="28.7109375" customWidth="1"/>
-    <col min="2" max="2" width="39.42578125" customWidth="1"/>
+    <col min="1" max="1" width="28.7265625" customWidth="1"/>
+    <col min="2" max="2" width="39.453125" customWidth="1"/>
     <col min="3" max="3" width="40" customWidth="1"/>
-    <col min="4" max="4" width="90.28515625" customWidth="1"/>
+    <col min="4" max="4" width="90.26953125" customWidth="1"/>
     <col min="5" max="5" width="88" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>187</v>
       </c>
@@ -1254,7 +1263,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -1265,7 +1274,7 @@
         <v>0.27200000000000002</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -1279,7 +1288,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1296,7 +1305,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>6</v>
       </c>
@@ -1313,7 +1322,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -1330,7 +1339,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>11</v>
       </c>
@@ -1347,7 +1356,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>14</v>
       </c>
@@ -1364,7 +1373,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>17</v>
       </c>
@@ -1381,7 +1390,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>20</v>
       </c>
@@ -1398,7 +1407,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>23</v>
       </c>
@@ -1415,7 +1424,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>26</v>
       </c>
@@ -1432,7 +1441,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>29</v>
       </c>
@@ -1449,7 +1458,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>32</v>
       </c>
@@ -1466,7 +1475,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>35</v>
       </c>
@@ -1483,7 +1492,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>38</v>
       </c>
@@ -1500,7 +1509,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>41</v>
       </c>
@@ -1517,7 +1526,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>44</v>
       </c>
@@ -1534,7 +1543,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>47</v>
       </c>
@@ -1551,7 +1560,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>50</v>
       </c>
@@ -1568,7 +1577,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>53</v>
       </c>
@@ -1585,7 +1594,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>56</v>
       </c>
@@ -1602,7 +1611,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>59</v>
       </c>
@@ -1619,7 +1628,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>61</v>
       </c>
@@ -1636,7 +1645,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>64</v>
       </c>
@@ -1653,7 +1662,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>67</v>
       </c>
@@ -1670,7 +1679,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>70</v>
       </c>
@@ -1687,7 +1696,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>73</v>
       </c>
@@ -1704,7 +1713,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>76</v>
       </c>
@@ -1721,7 +1730,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>79</v>
       </c>
@@ -1738,7 +1747,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>82</v>
       </c>
@@ -1755,7 +1764,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>85</v>
       </c>
@@ -1772,7 +1781,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>87</v>
       </c>
@@ -1789,7 +1798,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>90</v>
       </c>
@@ -1806,7 +1815,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>93</v>
       </c>
@@ -1823,7 +1832,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>96</v>
       </c>
@@ -1840,7 +1849,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>98</v>
       </c>
@@ -1857,7 +1866,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>101</v>
       </c>
@@ -1874,7 +1883,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>103</v>
       </c>
@@ -1891,7 +1900,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>105</v>
       </c>
@@ -1908,7 +1917,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>107</v>
       </c>
@@ -1925,7 +1934,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>109</v>
       </c>
@@ -1942,7 +1951,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>111</v>
       </c>
@@ -1959,7 +1968,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>113</v>
       </c>
@@ -1976,7 +1985,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>115</v>
       </c>
@@ -1993,7 +2002,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>117</v>
       </c>
@@ -2010,7 +2019,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>119</v>
       </c>
@@ -2027,7 +2036,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>121</v>
       </c>
@@ -2044,7 +2053,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>123</v>
       </c>
@@ -2061,7 +2070,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>126</v>
       </c>
@@ -2078,7 +2087,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>128</v>
       </c>
@@ -2095,7 +2104,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>130</v>
       </c>
@@ -2112,7 +2121,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>132</v>
       </c>
@@ -2129,7 +2138,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>134</v>
       </c>
@@ -2146,7 +2155,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>136</v>
       </c>
@@ -2163,7 +2172,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>138</v>
       </c>
@@ -2180,7 +2189,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
         <v>140</v>
       </c>
@@ -2197,7 +2206,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>142</v>
       </c>
@@ -2214,7 +2223,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
         <v>144</v>
       </c>
@@ -2231,7 +2240,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
         <v>146</v>
       </c>
@@ -2248,7 +2257,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
         <v>148</v>
       </c>
@@ -2265,7 +2274,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
         <v>150</v>
       </c>
@@ -2282,7 +2291,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
         <v>152</v>
       </c>
@@ -2299,7 +2308,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
         <v>154</v>
       </c>
@@ -2316,7 +2325,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
         <v>156</v>
       </c>
@@ -2333,7 +2342,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
         <v>159</v>
       </c>
@@ -2350,7 +2359,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
         <v>32</v>
       </c>
@@ -2367,7 +2376,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
         <v>35</v>
       </c>
@@ -2384,7 +2393,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
         <v>165</v>
       </c>
@@ -2401,7 +2410,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
         <v>38</v>
       </c>
@@ -2418,7 +2427,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
         <v>169</v>
       </c>
@@ -2435,7 +2444,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
         <v>172</v>
       </c>
@@ -2452,7 +2461,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
         <v>175</v>
       </c>
@@ -2469,7 +2478,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
         <v>178</v>
       </c>
@@ -2486,7 +2495,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
         <v>181</v>
       </c>
@@ -2503,7 +2512,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
         <v>184</v>
       </c>
@@ -2531,16 +2540,16 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4638B570-2779-4B7E-9323-189DFB4A8409}">
   <dimension ref="A1:E76"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="28.7109375" customWidth="1"/>
-    <col min="2" max="2" width="39.5703125" customWidth="1"/>
-    <col min="3" max="3" width="41.42578125" customWidth="1"/>
-    <col min="4" max="4" width="100.5703125" customWidth="1"/>
-    <col min="5" max="5" width="75.5703125" customWidth="1"/>
+    <col min="1" max="1" width="28.7265625" customWidth="1"/>
+    <col min="2" max="2" width="39.54296875" customWidth="1"/>
+    <col min="3" max="3" width="41.453125" customWidth="1"/>
+    <col min="4" max="4" width="100.54296875" customWidth="1"/>
+    <col min="5" max="5" width="75.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>187</v>
       </c>
@@ -2557,7 +2566,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -2568,7 +2577,7 @@
         <v>0.27200000000000002</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -2582,7 +2591,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -2599,7 +2608,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>6</v>
       </c>
@@ -2616,7 +2625,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -2633,7 +2642,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>11</v>
       </c>
@@ -2650,7 +2659,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>14</v>
       </c>
@@ -2667,7 +2676,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>17</v>
       </c>
@@ -2684,7 +2693,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>87</v>
       </c>
@@ -2701,77 +2710,77 @@
         <v>89</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>90</v>
-      </c>
-      <c r="B11" s="1">
-        <v>9.2299999999999999E-4</v>
+        <v>20</v>
+      </c>
+      <c r="B11">
+        <v>1E-3</v>
       </c>
       <c r="C11" s="1">
-        <v>9.2299999999999999E-4</v>
+        <v>4.3000000000000003E-6</v>
       </c>
       <c r="D11" t="s">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="E11" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>93</v>
-      </c>
-      <c r="B12" s="1">
-        <v>6.3700000000000003E-5</v>
+        <v>61</v>
+      </c>
+      <c r="B12">
+        <v>1E-3</v>
       </c>
       <c r="C12" s="1">
-        <v>6.3700000000000003E-5</v>
+        <v>5.6699999999999999E-6</v>
       </c>
       <c r="D12" t="s">
-        <v>94</v>
+        <v>62</v>
       </c>
       <c r="E12" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>20</v>
+        <v>64</v>
       </c>
       <c r="B13">
         <v>1E-3</v>
       </c>
-      <c r="C13" s="1">
-        <v>4.3000000000000003E-6</v>
+      <c r="C13">
+        <v>1E-3</v>
       </c>
       <c r="D13" t="s">
-        <v>21</v>
+        <v>65</v>
       </c>
       <c r="E13" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
+        <v>90</v>
+      </c>
+      <c r="B14" s="1">
+        <v>9.2299999999999999E-4</v>
+      </c>
+      <c r="C14" s="1">
+        <v>9.2299999999999999E-4</v>
+      </c>
+      <c r="D14" t="s">
+        <v>91</v>
+      </c>
+      <c r="E14" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
         <v>23</v>
-      </c>
-      <c r="B14" s="1">
-        <v>8.5999999999999998E-4</v>
-      </c>
-      <c r="C14">
-        <v>0</v>
-      </c>
-      <c r="D14" t="s">
-        <v>24</v>
-      </c>
-      <c r="E14" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>26</v>
       </c>
       <c r="B15" s="1">
         <v>8.5999999999999998E-4</v>
@@ -2780,15 +2789,15 @@
         <v>0</v>
       </c>
       <c r="D15" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="E15" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="B16" s="1">
         <v>8.5999999999999998E-4</v>
@@ -2797,15 +2806,15 @@
         <v>0</v>
       </c>
       <c r="D16" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="E16" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="B17" s="1">
         <v>8.5999999999999998E-4</v>
@@ -2814,523 +2823,523 @@
         <v>0</v>
       </c>
       <c r="D17" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="E17" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="B18" s="1">
         <v>8.5999999999999998E-4</v>
       </c>
-      <c r="C18" s="1">
+      <c r="C18">
+        <v>0</v>
+      </c>
+      <c r="D18" t="s">
+        <v>33</v>
+      </c>
+      <c r="E18" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
+        <v>35</v>
+      </c>
+      <c r="B19" s="1">
+        <v>8.5999999999999998E-4</v>
+      </c>
+      <c r="C19" s="1">
         <v>8.4500000000000005E-4</v>
       </c>
-      <c r="D18" t="s">
+      <c r="D19" t="s">
         <v>36</v>
       </c>
-      <c r="E18" t="s">
+      <c r="E19" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
+        <v>96</v>
+      </c>
+      <c r="B20" s="1">
+        <v>6.3699999999999998E-4</v>
+      </c>
+      <c r="C20" s="1">
+        <v>6.3699999999999998E-4</v>
+      </c>
+      <c r="D20" t="s">
+        <v>97</v>
+      </c>
+      <c r="E20" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
+        <v>82</v>
+      </c>
+      <c r="B21" s="1">
+        <v>6.0400000000000004E-4</v>
+      </c>
+      <c r="C21" s="1">
+        <v>6.0400000000000004E-4</v>
+      </c>
+      <c r="D21" t="s">
+        <v>83</v>
+      </c>
+      <c r="E21" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A22" t="s">
+        <v>156</v>
+      </c>
+      <c r="B22" s="1">
+        <v>5.9500000000000004E-4</v>
+      </c>
+      <c r="C22">
+        <v>0</v>
+      </c>
+      <c r="D22" t="s">
+        <v>157</v>
+      </c>
+      <c r="E22" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A23" t="s">
+        <v>159</v>
+      </c>
+      <c r="B23" s="1">
+        <v>5.9500000000000004E-4</v>
+      </c>
+      <c r="C23">
+        <v>0</v>
+      </c>
+      <c r="D23" t="s">
+        <v>160</v>
+      </c>
+      <c r="E23" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A24" t="s">
+        <v>32</v>
+      </c>
+      <c r="B24" s="1">
+        <v>5.9500000000000004E-4</v>
+      </c>
+      <c r="C24">
+        <v>0</v>
+      </c>
+      <c r="D24" t="s">
+        <v>161</v>
+      </c>
+      <c r="E24" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A25" t="s">
+        <v>35</v>
+      </c>
+      <c r="B25" s="1">
+        <v>5.9500000000000004E-4</v>
+      </c>
+      <c r="C25" s="1">
+        <v>5.9400000000000002E-4</v>
+      </c>
+      <c r="D25" t="s">
+        <v>163</v>
+      </c>
+      <c r="E25" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A26" t="s">
+        <v>85</v>
+      </c>
+      <c r="B26" s="1">
+        <v>3.4299999999999999E-4</v>
+      </c>
+      <c r="C26" s="1">
+        <v>3.4299999999999999E-4</v>
+      </c>
+      <c r="D26" t="s">
+        <v>86</v>
+      </c>
+      <c r="E26" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A27" t="s">
+        <v>98</v>
+      </c>
+      <c r="B27" s="1">
+        <v>1.6000000000000001E-4</v>
+      </c>
+      <c r="C27" s="1">
+        <v>1.6000000000000001E-4</v>
+      </c>
+      <c r="D27" t="s">
+        <v>99</v>
+      </c>
+      <c r="E27" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A28" t="s">
+        <v>117</v>
+      </c>
+      <c r="B28" s="1">
+        <v>1.4300000000000001E-4</v>
+      </c>
+      <c r="C28" s="1">
+        <v>1.4300000000000001E-4</v>
+      </c>
+      <c r="D28" t="s">
+        <v>118</v>
+      </c>
+      <c r="E28" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A29" t="s">
+        <v>169</v>
+      </c>
+      <c r="B29" s="1">
+        <v>1.3200000000000001E-4</v>
+      </c>
+      <c r="C29" s="1">
+        <v>1.3200000000000001E-4</v>
+      </c>
+      <c r="D29" t="s">
+        <v>170</v>
+      </c>
+      <c r="E29" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A30" t="s">
+        <v>115</v>
+      </c>
+      <c r="B30" s="1">
+        <v>1.25E-4</v>
+      </c>
+      <c r="C30" s="1">
+        <v>1.25E-4</v>
+      </c>
+      <c r="D30" t="s">
+        <v>116</v>
+      </c>
+      <c r="E30" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A31" t="s">
+        <v>128</v>
+      </c>
+      <c r="B31" s="1">
+        <v>1.05E-4</v>
+      </c>
+      <c r="C31" s="1">
+        <v>1.05E-4</v>
+      </c>
+      <c r="D31" t="s">
+        <v>129</v>
+      </c>
+      <c r="E31" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A32" t="s">
+        <v>70</v>
+      </c>
+      <c r="B32" s="1">
+        <v>6.8200000000000004E-5</v>
+      </c>
+      <c r="C32" s="1">
+        <v>6.8200000000000004E-5</v>
+      </c>
+      <c r="D32" t="s">
+        <v>71</v>
+      </c>
+      <c r="E32" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A33" t="s">
+        <v>93</v>
+      </c>
+      <c r="B33" s="1">
+        <v>6.3700000000000003E-5</v>
+      </c>
+      <c r="C33" s="1">
+        <v>6.3700000000000003E-5</v>
+      </c>
+      <c r="D33" t="s">
+        <v>94</v>
+      </c>
+      <c r="E33" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A34" t="s">
+        <v>41</v>
+      </c>
+      <c r="B34" s="1">
+        <v>4.9499999999999997E-5</v>
+      </c>
+      <c r="C34" s="1">
+        <v>4.9499999999999997E-5</v>
+      </c>
+      <c r="D34" t="s">
+        <v>42</v>
+      </c>
+      <c r="E34" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A35" t="s">
+        <v>67</v>
+      </c>
+      <c r="B35" s="1">
+        <v>3.9799999999999998E-5</v>
+      </c>
+      <c r="C35" s="1">
+        <v>3.9799999999999998E-5</v>
+      </c>
+      <c r="D35" t="s">
+        <v>68</v>
+      </c>
+      <c r="E35" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A36" t="s">
+        <v>105</v>
+      </c>
+      <c r="B36" s="1">
+        <v>3.8300000000000003E-5</v>
+      </c>
+      <c r="C36" s="1">
+        <v>3.8300000000000003E-5</v>
+      </c>
+      <c r="D36" t="s">
+        <v>106</v>
+      </c>
+      <c r="E36" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A37" t="s">
+        <v>101</v>
+      </c>
+      <c r="B37" s="1">
+        <v>3.2700000000000002E-5</v>
+      </c>
+      <c r="C37" s="1">
+        <v>3.2700000000000002E-5</v>
+      </c>
+      <c r="D37" t="s">
+        <v>102</v>
+      </c>
+      <c r="E37" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A38" t="s">
+        <v>53</v>
+      </c>
+      <c r="B38" s="1">
+        <v>3.2400000000000001E-5</v>
+      </c>
+      <c r="C38" s="1">
+        <v>3.2400000000000001E-5</v>
+      </c>
+      <c r="D38" t="s">
+        <v>54</v>
+      </c>
+      <c r="E38" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A39" t="s">
+        <v>50</v>
+      </c>
+      <c r="B39" s="1">
+        <v>3.2299999999999999E-5</v>
+      </c>
+      <c r="C39" s="1">
+        <v>3.2299999999999999E-5</v>
+      </c>
+      <c r="D39" t="s">
+        <v>51</v>
+      </c>
+      <c r="E39" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A40" t="s">
+        <v>109</v>
+      </c>
+      <c r="B40" s="1">
+        <v>3.01E-5</v>
+      </c>
+      <c r="C40" s="1">
+        <v>3.01E-5</v>
+      </c>
+      <c r="D40" t="s">
+        <v>110</v>
+      </c>
+      <c r="E40" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A41" t="s">
+        <v>121</v>
+      </c>
+      <c r="B41" s="1">
+        <v>2.9099999999999999E-5</v>
+      </c>
+      <c r="C41" s="1">
+        <v>2.9099999999999999E-5</v>
+      </c>
+      <c r="D41" t="s">
+        <v>122</v>
+      </c>
+      <c r="E41" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A42" t="s">
+        <v>172</v>
+      </c>
+      <c r="B42" s="1">
+        <v>2.5000000000000001E-5</v>
+      </c>
+      <c r="C42" s="1">
+        <v>2.5000000000000001E-5</v>
+      </c>
+      <c r="D42" t="s">
+        <v>173</v>
+      </c>
+      <c r="E42" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A43" t="s">
+        <v>44</v>
+      </c>
+      <c r="B43" s="1">
+        <v>2.02E-5</v>
+      </c>
+      <c r="C43" s="1">
+        <v>1.08E-5</v>
+      </c>
+      <c r="D43" t="s">
+        <v>45</v>
+      </c>
+      <c r="E43" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A44" t="s">
+        <v>107</v>
+      </c>
+      <c r="B44" s="1">
+        <v>1.8499999999999999E-5</v>
+      </c>
+      <c r="C44" s="1">
+        <v>1.8499999999999999E-5</v>
+      </c>
+      <c r="D44" t="s">
+        <v>108</v>
+      </c>
+      <c r="E44" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A45" t="s">
+        <v>111</v>
+      </c>
+      <c r="B45" s="1">
+        <v>1.63E-5</v>
+      </c>
+      <c r="C45" s="1">
+        <v>1.63E-5</v>
+      </c>
+      <c r="D45" t="s">
+        <v>112</v>
+      </c>
+      <c r="E45" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A46" t="s">
+        <v>103</v>
+      </c>
+      <c r="B46" s="1">
+        <v>1.52E-5</v>
+      </c>
+      <c r="C46" s="1">
+        <v>1.52E-5</v>
+      </c>
+      <c r="D46" t="s">
+        <v>104</v>
+      </c>
+      <c r="E46" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A47" t="s">
         <v>38</v>
       </c>
-      <c r="B19" s="1">
+      <c r="B47" s="1">
         <v>1.47E-5</v>
       </c>
-      <c r="C19" s="1">
+      <c r="C47" s="1">
         <v>1.47E-5</v>
       </c>
-      <c r="D19" t="s">
+      <c r="D47" t="s">
         <v>39</v>
       </c>
-      <c r="E19" t="s">
+      <c r="E47" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>41</v>
-      </c>
-      <c r="B20" s="1">
-        <v>4.9499999999999997E-5</v>
-      </c>
-      <c r="C20" s="1">
-        <v>4.9499999999999997E-5</v>
-      </c>
-      <c r="D20" t="s">
-        <v>42</v>
-      </c>
-      <c r="E20" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>53</v>
-      </c>
-      <c r="B21" s="1">
-        <v>3.2400000000000001E-5</v>
-      </c>
-      <c r="C21" s="1">
-        <v>3.2400000000000001E-5</v>
-      </c>
-      <c r="D21" t="s">
-        <v>54</v>
-      </c>
-      <c r="E21" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>50</v>
-      </c>
-      <c r="B22" s="1">
-        <v>3.2299999999999999E-5</v>
-      </c>
-      <c r="C22" s="1">
-        <v>3.2299999999999999E-5</v>
-      </c>
-      <c r="D22" t="s">
-        <v>51</v>
-      </c>
-      <c r="E22" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>44</v>
-      </c>
-      <c r="B23" s="1">
-        <v>2.02E-5</v>
-      </c>
-      <c r="C23" s="1">
-        <v>1.08E-5</v>
-      </c>
-      <c r="D23" t="s">
-        <v>45</v>
-      </c>
-      <c r="E23" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>47</v>
-      </c>
-      <c r="B24" s="1">
-        <v>9.3899999999999999E-6</v>
-      </c>
-      <c r="C24" s="1">
-        <v>9.3899999999999999E-6</v>
-      </c>
-      <c r="D24" t="s">
-        <v>48</v>
-      </c>
-      <c r="E24" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>59</v>
-      </c>
-      <c r="B25" s="1">
-        <v>7.7800000000000001E-6</v>
-      </c>
-      <c r="C25" s="1">
-        <v>7.7800000000000001E-6</v>
-      </c>
-      <c r="D25" t="s">
-        <v>60</v>
-      </c>
-      <c r="E25" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>56</v>
-      </c>
-      <c r="B26" s="1">
-        <v>1.42E-6</v>
-      </c>
-      <c r="C26" s="1">
-        <v>1.42E-6</v>
-      </c>
-      <c r="D26" t="s">
-        <v>57</v>
-      </c>
-      <c r="E26" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>61</v>
-      </c>
-      <c r="B27">
-        <v>1E-3</v>
-      </c>
-      <c r="C27" s="1">
-        <v>5.6699999999999999E-6</v>
-      </c>
-      <c r="D27" t="s">
-        <v>62</v>
-      </c>
-      <c r="E27" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>64</v>
-      </c>
-      <c r="B28">
-        <v>1E-3</v>
-      </c>
-      <c r="C28">
-        <v>1E-3</v>
-      </c>
-      <c r="D28" t="s">
-        <v>65</v>
-      </c>
-      <c r="E28" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>70</v>
-      </c>
-      <c r="B29" s="1">
-        <v>6.8200000000000004E-5</v>
-      </c>
-      <c r="C29" s="1">
-        <v>6.8200000000000004E-5</v>
-      </c>
-      <c r="D29" t="s">
-        <v>71</v>
-      </c>
-      <c r="E29" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>67</v>
-      </c>
-      <c r="B30" s="1">
-        <v>3.9799999999999998E-5</v>
-      </c>
-      <c r="C30" s="1">
-        <v>3.9799999999999998E-5</v>
-      </c>
-      <c r="D30" t="s">
-        <v>68</v>
-      </c>
-      <c r="E30" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>73</v>
-      </c>
-      <c r="B31" s="1">
-        <v>7.08E-6</v>
-      </c>
-      <c r="C31" s="1">
-        <v>7.08E-6</v>
-      </c>
-      <c r="D31" t="s">
-        <v>74</v>
-      </c>
-      <c r="E31" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
-        <v>76</v>
-      </c>
-      <c r="B32" s="1">
-        <v>3.1599999999999998E-6</v>
-      </c>
-      <c r="C32" s="1">
-        <v>3.1599999999999998E-6</v>
-      </c>
-      <c r="D32" t="s">
-        <v>77</v>
-      </c>
-      <c r="E32" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
-        <v>79</v>
-      </c>
-      <c r="B33" s="1">
-        <v>2.3E-6</v>
-      </c>
-      <c r="C33" s="1">
-        <v>2.3E-6</v>
-      </c>
-      <c r="D33" t="s">
-        <v>80</v>
-      </c>
-      <c r="E33" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
-        <v>96</v>
-      </c>
-      <c r="B34" s="1">
-        <v>6.3699999999999998E-4</v>
-      </c>
-      <c r="C34" s="1">
-        <v>6.3699999999999998E-4</v>
-      </c>
-      <c r="D34" t="s">
-        <v>97</v>
-      </c>
-      <c r="E34" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
-        <v>82</v>
-      </c>
-      <c r="B35" s="1">
-        <v>6.0400000000000004E-4</v>
-      </c>
-      <c r="C35" s="1">
-        <v>6.0400000000000004E-4</v>
-      </c>
-      <c r="D35" t="s">
-        <v>83</v>
-      </c>
-      <c r="E35" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
-        <v>85</v>
-      </c>
-      <c r="B36" s="1">
-        <v>3.4299999999999999E-4</v>
-      </c>
-      <c r="C36" s="1">
-        <v>3.4299999999999999E-4</v>
-      </c>
-      <c r="D36" t="s">
-        <v>86</v>
-      </c>
-      <c r="E36" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
-        <v>98</v>
-      </c>
-      <c r="B37" s="1">
-        <v>1.6000000000000001E-4</v>
-      </c>
-      <c r="C37" s="1">
-        <v>1.6000000000000001E-4</v>
-      </c>
-      <c r="D37" t="s">
-        <v>99</v>
-      </c>
-      <c r="E37" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
-        <v>117</v>
-      </c>
-      <c r="B38" s="1">
-        <v>1.4300000000000001E-4</v>
-      </c>
-      <c r="C38" s="1">
-        <v>1.4300000000000001E-4</v>
-      </c>
-      <c r="D38" t="s">
-        <v>118</v>
-      </c>
-      <c r="E38" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
-        <v>115</v>
-      </c>
-      <c r="B39" s="1">
-        <v>1.25E-4</v>
-      </c>
-      <c r="C39" s="1">
-        <v>1.25E-4</v>
-      </c>
-      <c r="D39" t="s">
-        <v>116</v>
-      </c>
-      <c r="E39" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
-        <v>128</v>
-      </c>
-      <c r="B40" s="1">
-        <v>1.05E-4</v>
-      </c>
-      <c r="C40" s="1">
-        <v>1.05E-4</v>
-      </c>
-      <c r="D40" t="s">
-        <v>129</v>
-      </c>
-      <c r="E40" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
-        <v>105</v>
-      </c>
-      <c r="B41" s="1">
-        <v>3.8300000000000003E-5</v>
-      </c>
-      <c r="C41" s="1">
-        <v>3.8300000000000003E-5</v>
-      </c>
-      <c r="D41" t="s">
-        <v>106</v>
-      </c>
-      <c r="E41" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
-        <v>101</v>
-      </c>
-      <c r="B42" s="1">
-        <v>3.2700000000000002E-5</v>
-      </c>
-      <c r="C42" s="1">
-        <v>3.2700000000000002E-5</v>
-      </c>
-      <c r="D42" t="s">
-        <v>102</v>
-      </c>
-      <c r="E42" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A43" t="s">
-        <v>109</v>
-      </c>
-      <c r="B43" s="1">
-        <v>3.01E-5</v>
-      </c>
-      <c r="C43" s="1">
-        <v>3.01E-5</v>
-      </c>
-      <c r="D43" t="s">
-        <v>110</v>
-      </c>
-      <c r="E43" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A44" t="s">
-        <v>121</v>
-      </c>
-      <c r="B44" s="1">
-        <v>2.9099999999999999E-5</v>
-      </c>
-      <c r="C44" s="1">
-        <v>2.9099999999999999E-5</v>
-      </c>
-      <c r="D44" t="s">
-        <v>122</v>
-      </c>
-      <c r="E44" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A45" t="s">
-        <v>107</v>
-      </c>
-      <c r="B45" s="1">
-        <v>1.8499999999999999E-5</v>
-      </c>
-      <c r="C45" s="1">
-        <v>1.8499999999999999E-5</v>
-      </c>
-      <c r="D45" t="s">
-        <v>108</v>
-      </c>
-      <c r="E45" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A46" t="s">
-        <v>111</v>
-      </c>
-      <c r="B46" s="1">
-        <v>1.63E-5</v>
-      </c>
-      <c r="C46" s="1">
-        <v>1.63E-5</v>
-      </c>
-      <c r="D46" t="s">
-        <v>112</v>
-      </c>
-      <c r="E46" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A47" t="s">
-        <v>103</v>
-      </c>
-      <c r="B47" s="1">
-        <v>1.52E-5</v>
-      </c>
-      <c r="C47" s="1">
-        <v>1.52E-5</v>
-      </c>
-      <c r="D47" t="s">
-        <v>104</v>
-      </c>
-      <c r="E47" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>130</v>
       </c>
@@ -3347,7 +3356,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>132</v>
       </c>
@@ -3364,7 +3373,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>113</v>
       </c>
@@ -3381,313 +3390,313 @@
         <v>84</v>
       </c>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
+        <v>47</v>
+      </c>
+      <c r="B51" s="1">
+        <v>9.3899999999999999E-6</v>
+      </c>
+      <c r="C51" s="1">
+        <v>9.3899999999999999E-6</v>
+      </c>
+      <c r="D51" t="s">
+        <v>48</v>
+      </c>
+      <c r="E51" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A52" t="s">
         <v>126</v>
       </c>
-      <c r="B51" s="1">
+      <c r="B52" s="1">
         <v>9.1800000000000002E-6</v>
       </c>
-      <c r="C51" s="1">
+      <c r="C52" s="1">
         <v>9.1800000000000002E-6</v>
       </c>
-      <c r="D51" t="s">
+      <c r="D52" t="s">
         <v>127</v>
       </c>
-      <c r="E51" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A52" t="s">
+      <c r="E52" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A53" t="s">
+        <v>59</v>
+      </c>
+      <c r="B53" s="1">
+        <v>7.7800000000000001E-6</v>
+      </c>
+      <c r="C53" s="1">
+        <v>7.7800000000000001E-6</v>
+      </c>
+      <c r="D53" t="s">
+        <v>60</v>
+      </c>
+      <c r="E53" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A54" t="s">
+        <v>73</v>
+      </c>
+      <c r="B54" s="1">
+        <v>7.08E-6</v>
+      </c>
+      <c r="C54" s="1">
+        <v>7.08E-6</v>
+      </c>
+      <c r="D54" t="s">
+        <v>74</v>
+      </c>
+      <c r="E54" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A55" t="s">
         <v>119</v>
       </c>
-      <c r="B52" s="1">
+      <c r="B55" s="1">
         <v>6.2899999999999999E-6</v>
       </c>
-      <c r="C52" s="1">
+      <c r="C55" s="1">
         <v>6.2899999999999999E-6</v>
       </c>
-      <c r="D52" t="s">
+      <c r="D55" t="s">
         <v>120</v>
       </c>
-      <c r="E52" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A53" t="s">
+      <c r="E55" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A56" t="s">
+        <v>76</v>
+      </c>
+      <c r="B56" s="1">
+        <v>3.1599999999999998E-6</v>
+      </c>
+      <c r="C56" s="1">
+        <v>3.1599999999999998E-6</v>
+      </c>
+      <c r="D56" t="s">
+        <v>77</v>
+      </c>
+      <c r="E56" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A57" t="s">
+        <v>79</v>
+      </c>
+      <c r="B57" s="1">
+        <v>2.3E-6</v>
+      </c>
+      <c r="C57" s="1">
+        <v>2.3E-6</v>
+      </c>
+      <c r="D57" t="s">
+        <v>80</v>
+      </c>
+      <c r="E57" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A58" t="s">
         <v>123</v>
       </c>
-      <c r="B53" s="1">
+      <c r="B58" s="1">
         <v>1.5600000000000001E-6</v>
       </c>
-      <c r="C53" s="1">
+      <c r="C58" s="1">
         <v>1.5600000000000001E-6</v>
       </c>
-      <c r="D53" t="s">
+      <c r="D58" t="s">
         <v>124</v>
-      </c>
-      <c r="E53" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A54" t="s">
-        <v>134</v>
-      </c>
-      <c r="B54" s="1">
-        <v>1.0100000000000001E-6</v>
-      </c>
-      <c r="C54" s="1">
-        <v>1.0100000000000001E-6</v>
-      </c>
-      <c r="D54" t="s">
-        <v>135</v>
-      </c>
-      <c r="E54" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A55" t="s">
-        <v>136</v>
-      </c>
-      <c r="B55" s="1">
-        <v>9.7300000000000004E-7</v>
-      </c>
-      <c r="C55" s="1">
-        <v>9.7300000000000004E-7</v>
-      </c>
-      <c r="D55" t="s">
-        <v>137</v>
-      </c>
-      <c r="E55" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A56" t="s">
-        <v>138</v>
-      </c>
-      <c r="B56" s="1">
-        <v>7.7800000000000001E-7</v>
-      </c>
-      <c r="C56" s="1">
-        <v>7.7800000000000001E-7</v>
-      </c>
-      <c r="D56" t="s">
-        <v>139</v>
-      </c>
-      <c r="E56" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A57" t="s">
-        <v>140</v>
-      </c>
-      <c r="B57" s="1">
-        <v>6.4600000000000004E-7</v>
-      </c>
-      <c r="C57" s="1">
-        <v>6.4600000000000004E-7</v>
-      </c>
-      <c r="D57" t="s">
-        <v>141</v>
-      </c>
-      <c r="E57" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A58" t="s">
-        <v>146</v>
-      </c>
-      <c r="B58" s="1">
-        <v>5.2600000000000002E-7</v>
-      </c>
-      <c r="C58" s="1">
-        <v>5.2600000000000002E-7</v>
-      </c>
-      <c r="D58" t="s">
-        <v>147</v>
       </c>
       <c r="E58" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
-        <v>148</v>
+        <v>56</v>
       </c>
       <c r="B59" s="1">
-        <v>5.2600000000000002E-7</v>
+        <v>1.42E-6</v>
       </c>
       <c r="C59" s="1">
-        <v>5.2600000000000002E-7</v>
+        <v>1.42E-6</v>
       </c>
       <c r="D59" t="s">
-        <v>149</v>
+        <v>57</v>
       </c>
       <c r="E59" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
-        <v>150</v>
+        <v>134</v>
       </c>
       <c r="B60" s="1">
-        <v>5.2600000000000002E-7</v>
+        <v>1.0100000000000001E-6</v>
       </c>
       <c r="C60" s="1">
-        <v>5.2600000000000002E-7</v>
+        <v>1.0100000000000001E-6</v>
       </c>
       <c r="D60" t="s">
-        <v>151</v>
+        <v>135</v>
       </c>
       <c r="E60" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
       <c r="B61" s="1">
-        <v>4.63E-7</v>
+        <v>9.7300000000000004E-7</v>
       </c>
       <c r="C61" s="1">
-        <v>4.63E-7</v>
+        <v>9.7300000000000004E-7</v>
       </c>
       <c r="D61" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="E61" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="B62" s="1">
-        <v>3.4499999999999998E-7</v>
+        <v>7.7800000000000001E-7</v>
       </c>
       <c r="C62" s="1">
-        <v>3.4499999999999998E-7</v>
+        <v>7.7800000000000001E-7</v>
       </c>
       <c r="D62" t="s">
-        <v>145</v>
+        <v>139</v>
       </c>
       <c r="E62" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
-        <v>152</v>
+        <v>140</v>
       </c>
       <c r="B63" s="1">
-        <v>2.9999999999999999E-7</v>
+        <v>6.4600000000000004E-7</v>
       </c>
       <c r="C63" s="1">
-        <v>2.9999999999999999E-7</v>
+        <v>6.4600000000000004E-7</v>
       </c>
       <c r="D63" t="s">
-        <v>153</v>
+        <v>141</v>
       </c>
       <c r="E63" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
-        <v>154</v>
+        <v>175</v>
       </c>
       <c r="B64" s="1">
-        <v>2.96E-7</v>
+        <v>5.5700000000000002E-7</v>
       </c>
       <c r="C64" s="1">
-        <v>2.96E-7</v>
+        <v>5.5700000000000002E-7</v>
       </c>
       <c r="D64" t="s">
-        <v>155</v>
+        <v>176</v>
       </c>
       <c r="E64" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A65" t="s">
+        <v>146</v>
+      </c>
+      <c r="B65" s="1">
+        <v>5.2600000000000002E-7</v>
+      </c>
+      <c r="C65" s="1">
+        <v>5.2600000000000002E-7</v>
+      </c>
+      <c r="D65" t="s">
+        <v>147</v>
+      </c>
+      <c r="E65" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A65" t="s">
-        <v>156</v>
-      </c>
-      <c r="B65" s="1">
-        <v>5.9500000000000004E-4</v>
-      </c>
-      <c r="C65">
-        <v>0</v>
-      </c>
-      <c r="D65" t="s">
-        <v>157</v>
-      </c>
-      <c r="E65" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
-        <v>159</v>
+        <v>148</v>
       </c>
       <c r="B66" s="1">
-        <v>5.9500000000000004E-4</v>
-      </c>
-      <c r="C66">
-        <v>0</v>
+        <v>5.2600000000000002E-7</v>
+      </c>
+      <c r="C66" s="1">
+        <v>5.2600000000000002E-7</v>
       </c>
       <c r="D66" t="s">
-        <v>160</v>
+        <v>149</v>
       </c>
       <c r="E66" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
-        <v>32</v>
+        <v>150</v>
       </c>
       <c r="B67" s="1">
-        <v>5.9500000000000004E-4</v>
-      </c>
-      <c r="C67">
-        <v>0</v>
+        <v>5.2600000000000002E-7</v>
+      </c>
+      <c r="C67" s="1">
+        <v>5.2600000000000002E-7</v>
       </c>
       <c r="D67" t="s">
-        <v>161</v>
+        <v>151</v>
       </c>
       <c r="E67" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
-        <v>35</v>
+        <v>142</v>
       </c>
       <c r="B68" s="1">
-        <v>5.9500000000000004E-4</v>
+        <v>4.63E-7</v>
       </c>
       <c r="C68" s="1">
-        <v>5.9400000000000002E-4</v>
+        <v>4.63E-7</v>
       </c>
       <c r="D68" t="s">
-        <v>163</v>
+        <v>143</v>
       </c>
       <c r="E68" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
         <v>165</v>
       </c>
@@ -3704,75 +3713,75 @@
         <v>167</v>
       </c>
     </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
+        <v>144</v>
+      </c>
+      <c r="B70" s="1">
+        <v>3.4499999999999998E-7</v>
+      </c>
+      <c r="C70" s="1">
+        <v>3.4499999999999998E-7</v>
+      </c>
+      <c r="D70" t="s">
+        <v>145</v>
+      </c>
+      <c r="E70" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A71" t="s">
+        <v>152</v>
+      </c>
+      <c r="B71" s="1">
+        <v>2.9999999999999999E-7</v>
+      </c>
+      <c r="C71" s="1">
+        <v>2.9999999999999999E-7</v>
+      </c>
+      <c r="D71" t="s">
+        <v>153</v>
+      </c>
+      <c r="E71" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A72" t="s">
+        <v>154</v>
+      </c>
+      <c r="B72" s="1">
+        <v>2.96E-7</v>
+      </c>
+      <c r="C72" s="1">
+        <v>2.96E-7</v>
+      </c>
+      <c r="D72" t="s">
+        <v>155</v>
+      </c>
+      <c r="E72" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A73" t="s">
         <v>38</v>
       </c>
-      <c r="B70" s="1">
+      <c r="B73" s="1">
         <v>5.1399999999999998E-10</v>
       </c>
-      <c r="C70" s="1">
+      <c r="C73" s="1">
         <v>5.1399999999999998E-10</v>
       </c>
-      <c r="D70" t="s">
+      <c r="D73" t="s">
         <v>168</v>
       </c>
-      <c r="E70" t="s">
+      <c r="E73" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A71" t="s">
-        <v>169</v>
-      </c>
-      <c r="B71" s="1">
-        <v>1.3200000000000001E-4</v>
-      </c>
-      <c r="C71" s="1">
-        <v>1.3200000000000001E-4</v>
-      </c>
-      <c r="D71" t="s">
-        <v>170</v>
-      </c>
-      <c r="E71" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A72" t="s">
-        <v>172</v>
-      </c>
-      <c r="B72" s="1">
-        <v>2.5000000000000001E-5</v>
-      </c>
-      <c r="C72" s="1">
-        <v>2.5000000000000001E-5</v>
-      </c>
-      <c r="D72" t="s">
-        <v>173</v>
-      </c>
-      <c r="E72" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A73" t="s">
-        <v>175</v>
-      </c>
-      <c r="B73" s="1">
-        <v>5.5700000000000002E-7</v>
-      </c>
-      <c r="C73" s="1">
-        <v>5.5700000000000002E-7</v>
-      </c>
-      <c r="D73" t="s">
-        <v>176</v>
-      </c>
-      <c r="E73" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
         <v>178</v>
       </c>
@@ -3789,7 +3798,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
         <v>181</v>
       </c>
@@ -3806,7 +3815,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
         <v>184</v>
       </c>
@@ -3834,16 +3843,16 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A3ABC9D8-4B40-4FB9-A55C-492FD91B1756}">
   <dimension ref="A1:E76"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="28.7109375" customWidth="1"/>
-    <col min="2" max="2" width="39.5703125" customWidth="1"/>
-    <col min="3" max="3" width="41.42578125" customWidth="1"/>
-    <col min="4" max="4" width="78.140625" customWidth="1"/>
-    <col min="5" max="5" width="57.85546875" customWidth="1"/>
+    <col min="1" max="1" width="28.7265625" customWidth="1"/>
+    <col min="2" max="2" width="39.54296875" customWidth="1"/>
+    <col min="3" max="3" width="41.453125" customWidth="1"/>
+    <col min="4" max="4" width="78.1796875" customWidth="1"/>
+    <col min="5" max="5" width="57.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>187</v>
       </c>
@@ -3860,7 +3869,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -3871,7 +3880,7 @@
         <v>0.27200000000000002</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -3885,7 +3894,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -3902,7 +3911,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>6</v>
       </c>
@@ -3919,7 +3928,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -3936,7 +3945,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>11</v>
       </c>
@@ -3953,7 +3962,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>14</v>
       </c>
@@ -3970,7 +3979,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>17</v>
       </c>
@@ -3987,7 +3996,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>20</v>
       </c>
@@ -4004,7 +4013,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>61</v>
       </c>
@@ -4021,7 +4030,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>64</v>
       </c>
@@ -4038,7 +4047,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>23</v>
       </c>
@@ -4055,7 +4064,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>26</v>
       </c>
@@ -4072,7 +4081,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>29</v>
       </c>
@@ -4089,7 +4098,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>32</v>
       </c>
@@ -4106,7 +4115,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>35</v>
       </c>
@@ -4123,7 +4132,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>82</v>
       </c>
@@ -4140,7 +4149,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>156</v>
       </c>
@@ -4157,7 +4166,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>159</v>
       </c>
@@ -4174,7 +4183,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>32</v>
       </c>
@@ -4191,7 +4200,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>35</v>
       </c>
@@ -4208,7 +4217,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>87</v>
       </c>
@@ -4225,7 +4234,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>90</v>
       </c>
@@ -4242,7 +4251,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>96</v>
       </c>
@@ -4259,7 +4268,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>85</v>
       </c>
@@ -4276,7 +4285,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>98</v>
       </c>
@@ -4293,7 +4302,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>169</v>
       </c>
@@ -4310,7 +4319,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>117</v>
       </c>
@@ -4327,7 +4336,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>70</v>
       </c>
@@ -4344,7 +4353,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>115</v>
       </c>
@@ -4361,7 +4370,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>41</v>
       </c>
@@ -4378,7 +4387,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>67</v>
       </c>
@@ -4395,7 +4404,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>128</v>
       </c>
@@ -4412,7 +4421,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>105</v>
       </c>
@@ -4429,7 +4438,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>93</v>
       </c>
@@ -4446,7 +4455,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>50</v>
       </c>
@@ -4463,7 +4472,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>44</v>
       </c>
@@ -4480,7 +4489,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>53</v>
       </c>
@@ -4497,7 +4506,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>109</v>
       </c>
@@ -4514,7 +4523,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>101</v>
       </c>
@@ -4531,7 +4540,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>38</v>
       </c>
@@ -4548,7 +4557,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>103</v>
       </c>
@@ -4565,7 +4574,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>107</v>
       </c>
@@ -4582,7 +4591,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>111</v>
       </c>
@@ -4599,7 +4608,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>121</v>
       </c>
@@ -4616,7 +4625,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>126</v>
       </c>
@@ -4633,7 +4642,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>47</v>
       </c>
@@ -4650,7 +4659,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>113</v>
       </c>
@@ -4667,7 +4676,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>172</v>
       </c>
@@ -4684,7 +4693,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>130</v>
       </c>
@@ -4701,7 +4710,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>132</v>
       </c>
@@ -4718,7 +4727,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>148</v>
       </c>
@@ -4735,7 +4744,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>150</v>
       </c>
@@ -4752,7 +4761,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>59</v>
       </c>
@@ -4769,7 +4778,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>119</v>
       </c>
@@ -4786,7 +4795,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
         <v>73</v>
       </c>
@@ -4803,7 +4812,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>79</v>
       </c>
@@ -4820,7 +4829,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
         <v>76</v>
       </c>
@@ -4837,7 +4846,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
         <v>154</v>
       </c>
@@ -4854,7 +4863,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
         <v>56</v>
       </c>
@@ -4871,7 +4880,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
         <v>123</v>
       </c>
@@ -4888,7 +4897,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
         <v>134</v>
       </c>
@@ -4905,7 +4914,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
         <v>136</v>
       </c>
@@ -4922,7 +4931,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
         <v>38</v>
       </c>
@@ -4939,7 +4948,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
         <v>165</v>
       </c>
@@ -4956,7 +4965,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
         <v>138</v>
       </c>
@@ -4973,7 +4982,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
         <v>140</v>
       </c>
@@ -4990,7 +4999,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
         <v>142</v>
       </c>
@@ -5007,7 +5016,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
         <v>152</v>
       </c>
@@ -5024,7 +5033,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
         <v>175</v>
       </c>
@@ -5041,7 +5050,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
         <v>146</v>
       </c>
@@ -5058,7 +5067,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
         <v>144</v>
       </c>
@@ -5075,7 +5084,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
         <v>178</v>
       </c>
@@ -5092,7 +5101,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
         <v>181</v>
       </c>
@@ -5109,7 +5118,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
         <v>184</v>
       </c>
@@ -5137,16 +5146,16 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E9342C08-D979-4FBE-81C9-BC1102F1F095}">
   <dimension ref="A1:E76"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="28.7109375" customWidth="1"/>
-    <col min="2" max="2" width="39.5703125" customWidth="1"/>
-    <col min="3" max="3" width="41.42578125" customWidth="1"/>
-    <col min="4" max="4" width="85.7109375" customWidth="1"/>
-    <col min="5" max="5" width="57.5703125" customWidth="1"/>
+    <col min="1" max="1" width="28.7265625" customWidth="1"/>
+    <col min="2" max="2" width="39.54296875" customWidth="1"/>
+    <col min="3" max="3" width="41.453125" customWidth="1"/>
+    <col min="4" max="4" width="85.7265625" customWidth="1"/>
+    <col min="5" max="5" width="57.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>187</v>
       </c>
@@ -5163,7 +5172,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -5174,7 +5183,7 @@
         <v>0.27200000000000002</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -5188,7 +5197,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -5205,7 +5214,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>6</v>
       </c>
@@ -5222,7 +5231,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -5239,7 +5248,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>11</v>
       </c>
@@ -5256,7 +5265,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>14</v>
       </c>
@@ -5273,7 +5282,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>17</v>
       </c>
@@ -5290,7 +5299,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>20</v>
       </c>
@@ -5307,60 +5316,60 @@
         <v>22</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
+        <v>61</v>
+      </c>
+      <c r="B11">
+        <v>1E-3</v>
+      </c>
+      <c r="C11" s="1">
+        <v>7.17E-6</v>
+      </c>
+      <c r="D11" t="s">
+        <v>62</v>
+      </c>
+      <c r="E11" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>64</v>
+      </c>
+      <c r="B12">
+        <v>1E-3</v>
+      </c>
+      <c r="C12">
+        <v>1E-3</v>
+      </c>
+      <c r="D12" t="s">
+        <v>65</v>
+      </c>
+      <c r="E12" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>87</v>
+      </c>
+      <c r="B13" s="1">
+        <v>9.1600000000000004E-4</v>
+      </c>
+      <c r="C13" s="1">
+        <v>9.7299999999999993E-5</v>
+      </c>
+      <c r="D13" t="s">
+        <v>88</v>
+      </c>
+      <c r="E13" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
         <v>23</v>
-      </c>
-      <c r="B11" s="1">
-        <v>8.7699999999999996E-4</v>
-      </c>
-      <c r="C11">
-        <v>0</v>
-      </c>
-      <c r="D11" t="s">
-        <v>24</v>
-      </c>
-      <c r="E11" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>26</v>
-      </c>
-      <c r="B12" s="1">
-        <v>8.7699999999999996E-4</v>
-      </c>
-      <c r="C12">
-        <v>0</v>
-      </c>
-      <c r="D12" t="s">
-        <v>27</v>
-      </c>
-      <c r="E12" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>29</v>
-      </c>
-      <c r="B13" s="1">
-        <v>8.7699999999999996E-4</v>
-      </c>
-      <c r="C13">
-        <v>0</v>
-      </c>
-      <c r="D13" t="s">
-        <v>30</v>
-      </c>
-      <c r="E13" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>32</v>
       </c>
       <c r="B14" s="1">
         <v>8.7699999999999996E-4</v>
@@ -5369,540 +5378,540 @@
         <v>0</v>
       </c>
       <c r="D14" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="E14" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="B15" s="1">
         <v>8.7699999999999996E-4</v>
       </c>
-      <c r="C15" s="1">
+      <c r="C15">
+        <v>0</v>
+      </c>
+      <c r="D15" t="s">
+        <v>27</v>
+      </c>
+      <c r="E15" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
+        <v>29</v>
+      </c>
+      <c r="B16" s="1">
+        <v>8.7699999999999996E-4</v>
+      </c>
+      <c r="C16">
+        <v>0</v>
+      </c>
+      <c r="D16" t="s">
+        <v>30</v>
+      </c>
+      <c r="E16" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
+        <v>32</v>
+      </c>
+      <c r="B17" s="1">
+        <v>8.7699999999999996E-4</v>
+      </c>
+      <c r="C17">
+        <v>0</v>
+      </c>
+      <c r="D17" t="s">
+        <v>33</v>
+      </c>
+      <c r="E17" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
+        <v>35</v>
+      </c>
+      <c r="B18" s="1">
+        <v>8.7699999999999996E-4</v>
+      </c>
+      <c r="C18" s="1">
         <v>8.52E-4</v>
       </c>
-      <c r="D15" t="s">
+      <c r="D18" t="s">
         <v>36</v>
       </c>
-      <c r="E15" t="s">
+      <c r="E18" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
+        <v>82</v>
+      </c>
+      <c r="B19" s="1">
+        <v>8.6399999999999997E-4</v>
+      </c>
+      <c r="C19" s="1">
+        <v>8.6399999999999997E-4</v>
+      </c>
+      <c r="D19" t="s">
+        <v>83</v>
+      </c>
+      <c r="E19" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
+        <v>90</v>
+      </c>
+      <c r="B20" s="1">
+        <v>7.6800000000000002E-4</v>
+      </c>
+      <c r="C20" s="1">
+        <v>7.6800000000000002E-4</v>
+      </c>
+      <c r="D20" t="s">
+        <v>91</v>
+      </c>
+      <c r="E20" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
+        <v>96</v>
+      </c>
+      <c r="B21" s="1">
+        <v>6.3100000000000005E-4</v>
+      </c>
+      <c r="C21" s="1">
+        <v>6.3100000000000005E-4</v>
+      </c>
+      <c r="D21" t="s">
+        <v>97</v>
+      </c>
+      <c r="E21" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A22" t="s">
+        <v>156</v>
+      </c>
+      <c r="B22" s="1">
+        <v>5.7200000000000003E-4</v>
+      </c>
+      <c r="C22">
+        <v>0</v>
+      </c>
+      <c r="D22" t="s">
+        <v>157</v>
+      </c>
+      <c r="E22" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A23" t="s">
+        <v>159</v>
+      </c>
+      <c r="B23" s="1">
+        <v>5.7200000000000003E-4</v>
+      </c>
+      <c r="C23">
+        <v>0</v>
+      </c>
+      <c r="D23" t="s">
+        <v>160</v>
+      </c>
+      <c r="E23" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A24" t="s">
+        <v>32</v>
+      </c>
+      <c r="B24" s="1">
+        <v>5.7200000000000003E-4</v>
+      </c>
+      <c r="C24">
+        <v>0</v>
+      </c>
+      <c r="D24" t="s">
+        <v>161</v>
+      </c>
+      <c r="E24" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A25" t="s">
+        <v>35</v>
+      </c>
+      <c r="B25" s="1">
+        <v>5.7200000000000003E-4</v>
+      </c>
+      <c r="C25" s="1">
+        <v>5.7200000000000003E-4</v>
+      </c>
+      <c r="D25" t="s">
+        <v>163</v>
+      </c>
+      <c r="E25" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A26" t="s">
+        <v>85</v>
+      </c>
+      <c r="B26" s="1">
+        <v>3.3399999999999999E-4</v>
+      </c>
+      <c r="C26" s="1">
+        <v>3.3399999999999999E-4</v>
+      </c>
+      <c r="D26" t="s">
+        <v>86</v>
+      </c>
+      <c r="E26" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A27" t="s">
+        <v>169</v>
+      </c>
+      <c r="B27" s="1">
+        <v>1.15E-4</v>
+      </c>
+      <c r="C27" s="1">
+        <v>1.15E-4</v>
+      </c>
+      <c r="D27" t="s">
+        <v>170</v>
+      </c>
+      <c r="E27" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A28" t="s">
+        <v>98</v>
+      </c>
+      <c r="B28" s="1">
+        <v>1.11E-4</v>
+      </c>
+      <c r="C28" s="1">
+        <v>1.11E-4</v>
+      </c>
+      <c r="D28" t="s">
+        <v>99</v>
+      </c>
+      <c r="E28" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A29" t="s">
+        <v>115</v>
+      </c>
+      <c r="B29" s="1">
+        <v>1.06E-4</v>
+      </c>
+      <c r="C29" s="1">
+        <v>1.06E-4</v>
+      </c>
+      <c r="D29" t="s">
+        <v>116</v>
+      </c>
+      <c r="E29" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A30" t="s">
+        <v>128</v>
+      </c>
+      <c r="B30" s="1">
+        <v>8.7700000000000004E-5</v>
+      </c>
+      <c r="C30" s="1">
+        <v>8.7700000000000004E-5</v>
+      </c>
+      <c r="D30" t="s">
+        <v>129</v>
+      </c>
+      <c r="E30" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A31" t="s">
+        <v>117</v>
+      </c>
+      <c r="B31" s="1">
+        <v>8.7499999999999999E-5</v>
+      </c>
+      <c r="C31" s="1">
+        <v>8.7499999999999999E-5</v>
+      </c>
+      <c r="D31" t="s">
+        <v>118</v>
+      </c>
+      <c r="E31" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A32" t="s">
+        <v>41</v>
+      </c>
+      <c r="B32" s="1">
+        <v>6.3299999999999994E-5</v>
+      </c>
+      <c r="C32" s="1">
+        <v>6.3299999999999994E-5</v>
+      </c>
+      <c r="D32" t="s">
+        <v>42</v>
+      </c>
+      <c r="E32" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A33" t="s">
+        <v>67</v>
+      </c>
+      <c r="B33" s="1">
+        <v>5.8199999999999998E-5</v>
+      </c>
+      <c r="C33" s="1">
+        <v>5.8199999999999998E-5</v>
+      </c>
+      <c r="D33" t="s">
+        <v>68</v>
+      </c>
+      <c r="E33" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A34" t="s">
+        <v>50</v>
+      </c>
+      <c r="B34" s="1">
+        <v>5.4799999999999997E-5</v>
+      </c>
+      <c r="C34" s="1">
+        <v>5.4799999999999997E-5</v>
+      </c>
+      <c r="D34" t="s">
+        <v>51</v>
+      </c>
+      <c r="E34" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A35" t="s">
+        <v>93</v>
+      </c>
+      <c r="B35" s="1">
+        <v>4.9700000000000002E-5</v>
+      </c>
+      <c r="C35" s="1">
+        <v>4.9700000000000002E-5</v>
+      </c>
+      <c r="D35" t="s">
+        <v>94</v>
+      </c>
+      <c r="E35" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A36" t="s">
+        <v>70</v>
+      </c>
+      <c r="B36" s="1">
+        <v>4.6300000000000001E-5</v>
+      </c>
+      <c r="C36" s="1">
+        <v>4.6300000000000001E-5</v>
+      </c>
+      <c r="D36" t="s">
+        <v>71</v>
+      </c>
+      <c r="E36" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A37" t="s">
+        <v>44</v>
+      </c>
+      <c r="B37" s="1">
+        <v>3.6600000000000002E-5</v>
+      </c>
+      <c r="C37" s="1">
+        <v>1.9700000000000001E-5</v>
+      </c>
+      <c r="D37" t="s">
+        <v>45</v>
+      </c>
+      <c r="E37" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A38" t="s">
+        <v>101</v>
+      </c>
+      <c r="B38" s="1">
+        <v>3.5800000000000003E-5</v>
+      </c>
+      <c r="C38" s="1">
+        <v>3.5800000000000003E-5</v>
+      </c>
+      <c r="D38" t="s">
+        <v>102</v>
+      </c>
+      <c r="E38" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A39" t="s">
+        <v>105</v>
+      </c>
+      <c r="B39" s="1">
+        <v>3.4499999999999998E-5</v>
+      </c>
+      <c r="C39" s="1">
+        <v>3.4499999999999998E-5</v>
+      </c>
+      <c r="D39" t="s">
+        <v>106</v>
+      </c>
+      <c r="E39" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A40" t="s">
+        <v>53</v>
+      </c>
+      <c r="B40" s="1">
+        <v>3.4199999999999998E-5</v>
+      </c>
+      <c r="C40" s="1">
+        <v>3.4199999999999998E-5</v>
+      </c>
+      <c r="D40" t="s">
+        <v>54</v>
+      </c>
+      <c r="E40" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A41" t="s">
+        <v>109</v>
+      </c>
+      <c r="B41" s="1">
+        <v>3.1199999999999999E-5</v>
+      </c>
+      <c r="C41" s="1">
+        <v>3.1199999999999999E-5</v>
+      </c>
+      <c r="D41" t="s">
+        <v>110</v>
+      </c>
+      <c r="E41" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A42" t="s">
+        <v>121</v>
+      </c>
+      <c r="B42" s="1">
+        <v>2.5999999999999998E-5</v>
+      </c>
+      <c r="C42" s="1">
+        <v>2.5999999999999998E-5</v>
+      </c>
+      <c r="D42" t="s">
+        <v>122</v>
+      </c>
+      <c r="E42" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A43" t="s">
         <v>38</v>
       </c>
-      <c r="B16" s="1">
+      <c r="B43" s="1">
         <v>2.55E-5</v>
       </c>
-      <c r="C16" s="1">
+      <c r="C43" s="1">
         <v>2.55E-5</v>
       </c>
-      <c r="D16" t="s">
+      <c r="D43" t="s">
         <v>39</v>
       </c>
-      <c r="E16" t="s">
+      <c r="E43" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>41</v>
-      </c>
-      <c r="B17" s="1">
-        <v>6.3299999999999994E-5</v>
-      </c>
-      <c r="C17" s="1">
-        <v>6.3299999999999994E-5</v>
-      </c>
-      <c r="D17" t="s">
-        <v>42</v>
-      </c>
-      <c r="E17" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>50</v>
-      </c>
-      <c r="B18" s="1">
-        <v>5.4799999999999997E-5</v>
-      </c>
-      <c r="C18" s="1">
-        <v>5.4799999999999997E-5</v>
-      </c>
-      <c r="D18" t="s">
-        <v>51</v>
-      </c>
-      <c r="E18" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>44</v>
-      </c>
-      <c r="B19" s="1">
-        <v>3.6600000000000002E-5</v>
-      </c>
-      <c r="C19" s="1">
-        <v>1.9700000000000001E-5</v>
-      </c>
-      <c r="D19" t="s">
-        <v>45</v>
-      </c>
-      <c r="E19" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>47</v>
-      </c>
-      <c r="B20" s="1">
-        <v>1.6900000000000001E-5</v>
-      </c>
-      <c r="C20" s="1">
-        <v>1.6900000000000001E-5</v>
-      </c>
-      <c r="D20" t="s">
-        <v>48</v>
-      </c>
-      <c r="E20" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>53</v>
-      </c>
-      <c r="B21" s="1">
-        <v>3.4199999999999998E-5</v>
-      </c>
-      <c r="C21" s="1">
-        <v>3.4199999999999998E-5</v>
-      </c>
-      <c r="D21" t="s">
-        <v>54</v>
-      </c>
-      <c r="E21" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>59</v>
-      </c>
-      <c r="B22" s="1">
-        <v>8.8799999999999997E-6</v>
-      </c>
-      <c r="C22" s="1">
-        <v>8.8799999999999997E-6</v>
-      </c>
-      <c r="D22" t="s">
-        <v>60</v>
-      </c>
-      <c r="E22" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>56</v>
-      </c>
-      <c r="B23" s="1">
-        <v>2.4200000000000001E-6</v>
-      </c>
-      <c r="C23" s="1">
-        <v>2.4200000000000001E-6</v>
-      </c>
-      <c r="D23" t="s">
-        <v>57</v>
-      </c>
-      <c r="E23" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>61</v>
-      </c>
-      <c r="B24">
-        <v>1E-3</v>
-      </c>
-      <c r="C24" s="1">
-        <v>7.17E-6</v>
-      </c>
-      <c r="D24" t="s">
-        <v>62</v>
-      </c>
-      <c r="E24" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>64</v>
-      </c>
-      <c r="B25">
-        <v>1E-3</v>
-      </c>
-      <c r="C25">
-        <v>1E-3</v>
-      </c>
-      <c r="D25" t="s">
-        <v>65</v>
-      </c>
-      <c r="E25" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>67</v>
-      </c>
-      <c r="B26" s="1">
-        <v>5.8199999999999998E-5</v>
-      </c>
-      <c r="C26" s="1">
-        <v>5.8199999999999998E-5</v>
-      </c>
-      <c r="D26" t="s">
-        <v>68</v>
-      </c>
-      <c r="E26" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>70</v>
-      </c>
-      <c r="B27" s="1">
-        <v>4.6300000000000001E-5</v>
-      </c>
-      <c r="C27" s="1">
-        <v>4.6300000000000001E-5</v>
-      </c>
-      <c r="D27" t="s">
-        <v>71</v>
-      </c>
-      <c r="E27" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>73</v>
-      </c>
-      <c r="B28" s="1">
-        <v>1.01E-5</v>
-      </c>
-      <c r="C28" s="1">
-        <v>1.01E-5</v>
-      </c>
-      <c r="D28" t="s">
-        <v>74</v>
-      </c>
-      <c r="E28" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>76</v>
-      </c>
-      <c r="B29" s="1">
-        <v>4.8099999999999997E-6</v>
-      </c>
-      <c r="C29" s="1">
-        <v>4.8099999999999997E-6</v>
-      </c>
-      <c r="D29" t="s">
-        <v>77</v>
-      </c>
-      <c r="E29" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>79</v>
-      </c>
-      <c r="B30" s="1">
-        <v>4.3000000000000003E-6</v>
-      </c>
-      <c r="C30" s="1">
-        <v>4.3000000000000003E-6</v>
-      </c>
-      <c r="D30" t="s">
-        <v>80</v>
-      </c>
-      <c r="E30" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>87</v>
-      </c>
-      <c r="B31" s="1">
-        <v>9.1600000000000004E-4</v>
-      </c>
-      <c r="C31" s="1">
-        <v>9.7299999999999993E-5</v>
-      </c>
-      <c r="D31" t="s">
-        <v>88</v>
-      </c>
-      <c r="E31" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
-        <v>90</v>
-      </c>
-      <c r="B32" s="1">
-        <v>7.6800000000000002E-4</v>
-      </c>
-      <c r="C32" s="1">
-        <v>7.6800000000000002E-4</v>
-      </c>
-      <c r="D32" t="s">
-        <v>91</v>
-      </c>
-      <c r="E32" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
-        <v>93</v>
-      </c>
-      <c r="B33" s="1">
-        <v>4.9700000000000002E-5</v>
-      </c>
-      <c r="C33" s="1">
-        <v>4.9700000000000002E-5</v>
-      </c>
-      <c r="D33" t="s">
-        <v>94</v>
-      </c>
-      <c r="E33" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
-        <v>82</v>
-      </c>
-      <c r="B34" s="1">
-        <v>8.6399999999999997E-4</v>
-      </c>
-      <c r="C34" s="1">
-        <v>8.6399999999999997E-4</v>
-      </c>
-      <c r="D34" t="s">
-        <v>83</v>
-      </c>
-      <c r="E34" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
-        <v>96</v>
-      </c>
-      <c r="B35" s="1">
-        <v>6.3100000000000005E-4</v>
-      </c>
-      <c r="C35" s="1">
-        <v>6.3100000000000005E-4</v>
-      </c>
-      <c r="D35" t="s">
-        <v>97</v>
-      </c>
-      <c r="E35" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
-        <v>85</v>
-      </c>
-      <c r="B36" s="1">
-        <v>3.3399999999999999E-4</v>
-      </c>
-      <c r="C36" s="1">
-        <v>3.3399999999999999E-4</v>
-      </c>
-      <c r="D36" t="s">
-        <v>86</v>
-      </c>
-      <c r="E36" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
-        <v>98</v>
-      </c>
-      <c r="B37" s="1">
-        <v>1.11E-4</v>
-      </c>
-      <c r="C37" s="1">
-        <v>1.11E-4</v>
-      </c>
-      <c r="D37" t="s">
-        <v>99</v>
-      </c>
-      <c r="E37" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
-        <v>115</v>
-      </c>
-      <c r="B38" s="1">
-        <v>1.06E-4</v>
-      </c>
-      <c r="C38" s="1">
-        <v>1.06E-4</v>
-      </c>
-      <c r="D38" t="s">
-        <v>116</v>
-      </c>
-      <c r="E38" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
-        <v>128</v>
-      </c>
-      <c r="B39" s="1">
-        <v>8.7700000000000004E-5</v>
-      </c>
-      <c r="C39" s="1">
-        <v>8.7700000000000004E-5</v>
-      </c>
-      <c r="D39" t="s">
-        <v>129</v>
-      </c>
-      <c r="E39" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
-        <v>117</v>
-      </c>
-      <c r="B40" s="1">
-        <v>8.7499999999999999E-5</v>
-      </c>
-      <c r="C40" s="1">
-        <v>8.7499999999999999E-5</v>
-      </c>
-      <c r="D40" t="s">
-        <v>118</v>
-      </c>
-      <c r="E40" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
-        <v>101</v>
-      </c>
-      <c r="B41" s="1">
-        <v>3.5800000000000003E-5</v>
-      </c>
-      <c r="C41" s="1">
-        <v>3.5800000000000003E-5</v>
-      </c>
-      <c r="D41" t="s">
-        <v>102</v>
-      </c>
-      <c r="E41" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
-        <v>105</v>
-      </c>
-      <c r="B42" s="1">
-        <v>3.4499999999999998E-5</v>
-      </c>
-      <c r="C42" s="1">
-        <v>3.4499999999999998E-5</v>
-      </c>
-      <c r="D42" t="s">
-        <v>106</v>
-      </c>
-      <c r="E42" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A43" t="s">
-        <v>109</v>
-      </c>
-      <c r="B43" s="1">
-        <v>3.1199999999999999E-5</v>
-      </c>
-      <c r="C43" s="1">
-        <v>3.1199999999999999E-5</v>
-      </c>
-      <c r="D43" t="s">
-        <v>110</v>
-      </c>
-      <c r="E43" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
-        <v>121</v>
+        <v>103</v>
       </c>
       <c r="B44" s="1">
-        <v>2.5999999999999998E-5</v>
+        <v>2.23E-5</v>
       </c>
       <c r="C44" s="1">
-        <v>2.5999999999999998E-5</v>
+        <v>2.23E-5</v>
       </c>
       <c r="D44" t="s">
-        <v>122</v>
+        <v>104</v>
       </c>
       <c r="E44" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
-        <v>103</v>
+        <v>172</v>
       </c>
       <c r="B45" s="1">
-        <v>2.23E-5</v>
+        <v>2.0699999999999998E-5</v>
       </c>
       <c r="C45" s="1">
-        <v>2.23E-5</v>
+        <v>2.0699999999999998E-5</v>
       </c>
       <c r="D45" t="s">
-        <v>104</v>
+        <v>173</v>
       </c>
       <c r="E45" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>107</v>
       </c>
@@ -5919,7 +5928,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>111</v>
       </c>
@@ -5936,7 +5945,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>113</v>
       </c>
@@ -5953,432 +5962,432 @@
         <v>84</v>
       </c>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
+        <v>47</v>
+      </c>
+      <c r="B49" s="1">
+        <v>1.6900000000000001E-5</v>
+      </c>
+      <c r="C49" s="1">
+        <v>1.6900000000000001E-5</v>
+      </c>
+      <c r="D49" t="s">
+        <v>48</v>
+      </c>
+      <c r="E49" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A50" t="s">
         <v>130</v>
       </c>
-      <c r="B49" s="1">
+      <c r="B50" s="1">
         <v>1.5500000000000001E-5</v>
       </c>
-      <c r="C49" s="1">
+      <c r="C50" s="1">
         <v>1.5500000000000001E-5</v>
       </c>
-      <c r="D49" t="s">
+      <c r="D50" t="s">
         <v>131</v>
       </c>
-      <c r="E49" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A50" t="s">
+      <c r="E50" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A51" t="s">
         <v>132</v>
       </c>
-      <c r="B50" s="1">
+      <c r="B51" s="1">
         <v>1.19E-5</v>
       </c>
-      <c r="C50" s="1">
+      <c r="C51" s="1">
         <v>1.19E-5</v>
       </c>
-      <c r="D50" t="s">
+      <c r="D51" t="s">
         <v>133</v>
       </c>
-      <c r="E50" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A51" t="s">
+      <c r="E51" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A52" t="s">
+        <v>73</v>
+      </c>
+      <c r="B52" s="1">
+        <v>1.01E-5</v>
+      </c>
+      <c r="C52" s="1">
+        <v>1.01E-5</v>
+      </c>
+      <c r="D52" t="s">
+        <v>74</v>
+      </c>
+      <c r="E52" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A53" t="s">
         <v>119</v>
       </c>
-      <c r="B51" s="1">
+      <c r="B53" s="1">
         <v>9.4099999999999997E-6</v>
       </c>
-      <c r="C51" s="1">
+      <c r="C53" s="1">
         <v>9.4099999999999997E-6</v>
       </c>
-      <c r="D51" t="s">
+      <c r="D53" t="s">
         <v>120</v>
       </c>
-      <c r="E51" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A52" t="s">
+      <c r="E53" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A54" t="s">
         <v>126</v>
       </c>
-      <c r="B52" s="1">
+      <c r="B54" s="1">
         <v>9.1800000000000002E-6</v>
       </c>
-      <c r="C52" s="1">
+      <c r="C54" s="1">
         <v>9.1800000000000002E-6</v>
       </c>
-      <c r="D52" t="s">
+      <c r="D54" t="s">
         <v>127</v>
       </c>
-      <c r="E52" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A53" t="s">
+      <c r="E54" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A55" t="s">
+        <v>59</v>
+      </c>
+      <c r="B55" s="1">
+        <v>8.8799999999999997E-6</v>
+      </c>
+      <c r="C55" s="1">
+        <v>8.8799999999999997E-6</v>
+      </c>
+      <c r="D55" t="s">
+        <v>60</v>
+      </c>
+      <c r="E55" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A56" t="s">
+        <v>76</v>
+      </c>
+      <c r="B56" s="1">
+        <v>4.8099999999999997E-6</v>
+      </c>
+      <c r="C56" s="1">
+        <v>4.8099999999999997E-6</v>
+      </c>
+      <c r="D56" t="s">
+        <v>77</v>
+      </c>
+      <c r="E56" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A57" t="s">
+        <v>79</v>
+      </c>
+      <c r="B57" s="1">
+        <v>4.3000000000000003E-6</v>
+      </c>
+      <c r="C57" s="1">
+        <v>4.3000000000000003E-6</v>
+      </c>
+      <c r="D57" t="s">
+        <v>80</v>
+      </c>
+      <c r="E57" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A58" t="s">
         <v>123</v>
       </c>
-      <c r="B53" s="1">
+      <c r="B58" s="1">
         <v>4.0500000000000002E-6</v>
       </c>
-      <c r="C53" s="1">
+      <c r="C58" s="1">
         <v>4.0500000000000002E-6</v>
       </c>
-      <c r="D53" t="s">
+      <c r="D58" t="s">
         <v>124</v>
-      </c>
-      <c r="E53" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A54" t="s">
-        <v>134</v>
-      </c>
-      <c r="B54" s="1">
-        <v>2.7199999999999998E-6</v>
-      </c>
-      <c r="C54" s="1">
-        <v>2.7199999999999998E-6</v>
-      </c>
-      <c r="D54" t="s">
-        <v>135</v>
-      </c>
-      <c r="E54" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A55" t="s">
-        <v>136</v>
-      </c>
-      <c r="B55" s="1">
-        <v>2.5900000000000002E-6</v>
-      </c>
-      <c r="C55" s="1">
-        <v>2.5900000000000002E-6</v>
-      </c>
-      <c r="D55" t="s">
-        <v>137</v>
-      </c>
-      <c r="E55" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A56" t="s">
-        <v>138</v>
-      </c>
-      <c r="B56" s="1">
-        <v>1.9199999999999998E-6</v>
-      </c>
-      <c r="C56" s="1">
-        <v>1.9199999999999998E-6</v>
-      </c>
-      <c r="D56" t="s">
-        <v>139</v>
-      </c>
-      <c r="E56" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A57" t="s">
-        <v>140</v>
-      </c>
-      <c r="B57" s="1">
-        <v>8.8700000000000004E-7</v>
-      </c>
-      <c r="C57" s="1">
-        <v>8.8700000000000004E-7</v>
-      </c>
-      <c r="D57" t="s">
-        <v>141</v>
-      </c>
-      <c r="E57" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A58" t="s">
-        <v>142</v>
-      </c>
-      <c r="B58" s="1">
-        <v>5.7800000000000001E-7</v>
-      </c>
-      <c r="C58" s="1">
-        <v>5.7800000000000001E-7</v>
-      </c>
-      <c r="D58" t="s">
-        <v>143</v>
       </c>
       <c r="E58" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
-        <v>146</v>
+        <v>134</v>
       </c>
       <c r="B59" s="1">
-        <v>5.2600000000000002E-7</v>
+        <v>2.7199999999999998E-6</v>
       </c>
       <c r="C59" s="1">
-        <v>5.2600000000000002E-7</v>
+        <v>2.7199999999999998E-6</v>
       </c>
       <c r="D59" t="s">
-        <v>147</v>
+        <v>135</v>
       </c>
       <c r="E59" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
-        <v>148</v>
+        <v>136</v>
       </c>
       <c r="B60" s="1">
-        <v>5.2600000000000002E-7</v>
+        <v>2.5900000000000002E-6</v>
       </c>
       <c r="C60" s="1">
-        <v>5.2600000000000002E-7</v>
+        <v>2.5900000000000002E-6</v>
       </c>
       <c r="D60" t="s">
-        <v>149</v>
+        <v>137</v>
       </c>
       <c r="E60" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
-        <v>150</v>
+        <v>56</v>
       </c>
       <c r="B61" s="1">
-        <v>5.2600000000000002E-7</v>
+        <v>2.4200000000000001E-6</v>
       </c>
       <c r="C61" s="1">
-        <v>5.2600000000000002E-7</v>
+        <v>2.4200000000000001E-6</v>
       </c>
       <c r="D61" t="s">
-        <v>151</v>
+        <v>57</v>
       </c>
       <c r="E61" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A62" t="s">
+        <v>138</v>
+      </c>
+      <c r="B62" s="1">
+        <v>1.9199999999999998E-6</v>
+      </c>
+      <c r="C62" s="1">
+        <v>1.9199999999999998E-6</v>
+      </c>
+      <c r="D62" t="s">
+        <v>139</v>
+      </c>
+      <c r="E62" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A62" t="s">
-        <v>144</v>
-      </c>
-      <c r="B62" s="1">
-        <v>4.6899999999999998E-7</v>
-      </c>
-      <c r="C62" s="1">
-        <v>4.6899999999999998E-7</v>
-      </c>
-      <c r="D62" t="s">
-        <v>145</v>
-      </c>
-      <c r="E62" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
-        <v>152</v>
+        <v>140</v>
       </c>
       <c r="B63" s="1">
-        <v>2.9999999999999999E-7</v>
+        <v>8.8700000000000004E-7</v>
       </c>
       <c r="C63" s="1">
-        <v>2.9999999999999999E-7</v>
+        <v>8.8700000000000004E-7</v>
       </c>
       <c r="D63" t="s">
-        <v>153</v>
+        <v>141</v>
       </c>
       <c r="E63" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
-        <v>154</v>
+        <v>142</v>
       </c>
       <c r="B64" s="1">
-        <v>2.96E-7</v>
+        <v>5.7800000000000001E-7</v>
       </c>
       <c r="C64" s="1">
-        <v>2.96E-7</v>
+        <v>5.7800000000000001E-7</v>
       </c>
       <c r="D64" t="s">
-        <v>155</v>
+        <v>143</v>
       </c>
       <c r="E64" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
-        <v>156</v>
+        <v>175</v>
       </c>
       <c r="B65" s="1">
-        <v>5.7200000000000003E-4</v>
-      </c>
-      <c r="C65">
-        <v>0</v>
+        <v>5.5700000000000002E-7</v>
+      </c>
+      <c r="C65" s="1">
+        <v>5.5700000000000002E-7</v>
       </c>
       <c r="D65" t="s">
-        <v>157</v>
+        <v>176</v>
       </c>
       <c r="E65" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
-        <v>159</v>
+        <v>146</v>
       </c>
       <c r="B66" s="1">
-        <v>5.7200000000000003E-4</v>
-      </c>
-      <c r="C66">
-        <v>0</v>
+        <v>5.2600000000000002E-7</v>
+      </c>
+      <c r="C66" s="1">
+        <v>5.2600000000000002E-7</v>
       </c>
       <c r="D66" t="s">
-        <v>160</v>
+        <v>147</v>
       </c>
       <c r="E66" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
-        <v>32</v>
+        <v>148</v>
       </c>
       <c r="B67" s="1">
-        <v>5.7200000000000003E-4</v>
-      </c>
-      <c r="C67">
-        <v>0</v>
+        <v>5.2600000000000002E-7</v>
+      </c>
+      <c r="C67" s="1">
+        <v>5.2600000000000002E-7</v>
       </c>
       <c r="D67" t="s">
-        <v>161</v>
+        <v>149</v>
       </c>
       <c r="E67" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
-        <v>35</v>
+        <v>150</v>
       </c>
       <c r="B68" s="1">
-        <v>5.7200000000000003E-4</v>
+        <v>5.2600000000000002E-7</v>
       </c>
       <c r="C68" s="1">
-        <v>5.7200000000000003E-4</v>
+        <v>5.2600000000000002E-7</v>
       </c>
       <c r="D68" t="s">
-        <v>163</v>
+        <v>151</v>
       </c>
       <c r="E68" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
+        <v>144</v>
+      </c>
+      <c r="B69" s="1">
+        <v>4.6899999999999998E-7</v>
+      </c>
+      <c r="C69" s="1">
+        <v>4.6899999999999998E-7</v>
+      </c>
+      <c r="D69" t="s">
+        <v>145</v>
+      </c>
+      <c r="E69" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A70" t="s">
         <v>165</v>
       </c>
-      <c r="B69" s="1">
+      <c r="B70" s="1">
         <v>3.8700000000000001E-7</v>
       </c>
-      <c r="C69" s="1">
+      <c r="C70" s="1">
         <v>3.8700000000000001E-7</v>
       </c>
-      <c r="D69" t="s">
+      <c r="D70" t="s">
         <v>166</v>
       </c>
-      <c r="E69" t="s">
+      <c r="E70" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A70" t="s">
+    <row r="71" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A71" t="s">
+        <v>152</v>
+      </c>
+      <c r="B71" s="1">
+        <v>2.9999999999999999E-7</v>
+      </c>
+      <c r="C71" s="1">
+        <v>2.9999999999999999E-7</v>
+      </c>
+      <c r="D71" t="s">
+        <v>153</v>
+      </c>
+      <c r="E71" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A72" t="s">
+        <v>154</v>
+      </c>
+      <c r="B72" s="1">
+        <v>2.96E-7</v>
+      </c>
+      <c r="C72" s="1">
+        <v>2.96E-7</v>
+      </c>
+      <c r="D72" t="s">
+        <v>155</v>
+      </c>
+      <c r="E72" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A73" t="s">
         <v>38</v>
       </c>
-      <c r="B70" s="1">
+      <c r="B73" s="1">
         <v>5.1399999999999998E-10</v>
       </c>
-      <c r="C70" s="1">
+      <c r="C73" s="1">
         <v>5.1399999999999998E-10</v>
       </c>
-      <c r="D70" t="s">
+      <c r="D73" t="s">
         <v>168</v>
       </c>
-      <c r="E70" t="s">
+      <c r="E73" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A71" t="s">
-        <v>169</v>
-      </c>
-      <c r="B71" s="1">
-        <v>1.15E-4</v>
-      </c>
-      <c r="C71" s="1">
-        <v>1.15E-4</v>
-      </c>
-      <c r="D71" t="s">
-        <v>170</v>
-      </c>
-      <c r="E71" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A72" t="s">
-        <v>172</v>
-      </c>
-      <c r="B72" s="1">
-        <v>2.0699999999999998E-5</v>
-      </c>
-      <c r="C72" s="1">
-        <v>2.0699999999999998E-5</v>
-      </c>
-      <c r="D72" t="s">
-        <v>173</v>
-      </c>
-      <c r="E72" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A73" t="s">
-        <v>175</v>
-      </c>
-      <c r="B73" s="1">
-        <v>5.5700000000000002E-7</v>
-      </c>
-      <c r="C73" s="1">
-        <v>5.5700000000000002E-7</v>
-      </c>
-      <c r="D73" t="s">
-        <v>176</v>
-      </c>
-      <c r="E73" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
         <v>178</v>
       </c>
@@ -6395,7 +6404,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
         <v>181</v>
       </c>
@@ -6412,7 +6421,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
         <v>184</v>
       </c>
@@ -6440,16 +6449,16 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BAE15965-3211-4FBB-8692-E47112645D65}">
   <dimension ref="A1:E76"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="28.7109375" customWidth="1"/>
-    <col min="2" max="2" width="39.5703125" customWidth="1"/>
-    <col min="3" max="3" width="41.42578125" customWidth="1"/>
-    <col min="4" max="4" width="96.7109375" customWidth="1"/>
-    <col min="5" max="5" width="57.42578125" customWidth="1"/>
+    <col min="1" max="1" width="28.7265625" customWidth="1"/>
+    <col min="2" max="2" width="39.54296875" customWidth="1"/>
+    <col min="3" max="3" width="41.453125" customWidth="1"/>
+    <col min="4" max="4" width="96.7265625" customWidth="1"/>
+    <col min="5" max="5" width="57.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>187</v>
       </c>
@@ -6466,7 +6475,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -6477,7 +6486,7 @@
         <v>0.27200000000000002</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -6491,7 +6500,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -6508,7 +6517,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>6</v>
       </c>
@@ -6525,7 +6534,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -6542,7 +6551,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>11</v>
       </c>
@@ -6559,7 +6568,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>14</v>
       </c>
@@ -6576,7 +6585,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>17</v>
       </c>
@@ -6593,7 +6602,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>20</v>
       </c>
@@ -6610,26 +6619,26 @@
         <v>22</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
+        <v>61</v>
+      </c>
+      <c r="B11" s="1">
+        <v>8.6799999999999996E-4</v>
+      </c>
+      <c r="C11" s="1">
+        <v>5.2599999999999996E-6</v>
+      </c>
+      <c r="D11" t="s">
+        <v>62</v>
+      </c>
+      <c r="E11" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
         <v>23</v>
-      </c>
-      <c r="B11" s="1">
-        <v>7.6199999999999998E-4</v>
-      </c>
-      <c r="C11">
-        <v>0</v>
-      </c>
-      <c r="D11" t="s">
-        <v>24</v>
-      </c>
-      <c r="E11" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>26</v>
       </c>
       <c r="B12" s="1">
         <v>7.6199999999999998E-4</v>
@@ -6638,15 +6647,15 @@
         <v>0</v>
       </c>
       <c r="D12" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="E12" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="B13" s="1">
         <v>7.6199999999999998E-4</v>
@@ -6655,15 +6664,15 @@
         <v>0</v>
       </c>
       <c r="D13" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="E13" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="B14" s="1">
         <v>7.6199999999999998E-4</v>
@@ -6672,319 +6681,319 @@
         <v>0</v>
       </c>
       <c r="D14" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="E14" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="B15" s="1">
         <v>7.6199999999999998E-4</v>
       </c>
-      <c r="C15" s="1">
+      <c r="C15">
+        <v>0</v>
+      </c>
+      <c r="D15" t="s">
+        <v>33</v>
+      </c>
+      <c r="E15" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
+        <v>35</v>
+      </c>
+      <c r="B16" s="1">
+        <v>7.6199999999999998E-4</v>
+      </c>
+      <c r="C16" s="1">
         <v>7.4399999999999998E-4</v>
       </c>
-      <c r="D15" t="s">
+      <c r="D16" t="s">
         <v>36</v>
       </c>
-      <c r="E15" t="s">
+      <c r="E16" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>38</v>
-      </c>
-      <c r="B16" s="1">
-        <v>1.7799999999999999E-5</v>
-      </c>
-      <c r="C16" s="1">
-        <v>1.7799999999999999E-5</v>
-      </c>
-      <c r="D16" t="s">
-        <v>39</v>
-      </c>
-      <c r="E16" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
+        <v>64</v>
+      </c>
+      <c r="B17" s="1">
+        <v>7.3899999999999997E-4</v>
+      </c>
+      <c r="C17" s="1">
+        <v>7.3899999999999997E-4</v>
+      </c>
+      <c r="D17" t="s">
+        <v>65</v>
+      </c>
+      <c r="E17" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
+        <v>156</v>
+      </c>
+      <c r="B18" s="1">
+        <v>7.0699999999999995E-4</v>
+      </c>
+      <c r="C18">
+        <v>0</v>
+      </c>
+      <c r="D18" t="s">
+        <v>157</v>
+      </c>
+      <c r="E18" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
+        <v>159</v>
+      </c>
+      <c r="B19" s="1">
+        <v>7.0699999999999995E-4</v>
+      </c>
+      <c r="C19">
+        <v>0</v>
+      </c>
+      <c r="D19" t="s">
+        <v>160</v>
+      </c>
+      <c r="E19" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
+        <v>32</v>
+      </c>
+      <c r="B20" s="1">
+        <v>7.0699999999999995E-4</v>
+      </c>
+      <c r="C20">
+        <v>0</v>
+      </c>
+      <c r="D20" t="s">
+        <v>161</v>
+      </c>
+      <c r="E20" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
+        <v>35</v>
+      </c>
+      <c r="B21" s="1">
+        <v>7.0699999999999995E-4</v>
+      </c>
+      <c r="C21" s="1">
+        <v>7.0200000000000004E-4</v>
+      </c>
+      <c r="D21" t="s">
+        <v>163</v>
+      </c>
+      <c r="E21" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A22" t="s">
+        <v>87</v>
+      </c>
+      <c r="B22" s="1">
+        <v>6.5700000000000003E-4</v>
+      </c>
+      <c r="C22" s="1">
+        <v>1.02E-4</v>
+      </c>
+      <c r="D22" t="s">
+        <v>88</v>
+      </c>
+      <c r="E22" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A23" t="s">
+        <v>90</v>
+      </c>
+      <c r="B23" s="1">
+        <v>5.1099999999999995E-4</v>
+      </c>
+      <c r="C23" s="1">
+        <v>5.1099999999999995E-4</v>
+      </c>
+      <c r="D23" t="s">
+        <v>91</v>
+      </c>
+      <c r="E23" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A24" t="s">
+        <v>82</v>
+      </c>
+      <c r="B24" s="1">
+        <v>3.9300000000000001E-4</v>
+      </c>
+      <c r="C24" s="1">
+        <v>3.9300000000000001E-4</v>
+      </c>
+      <c r="D24" t="s">
+        <v>83</v>
+      </c>
+      <c r="E24" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A25" t="s">
+        <v>96</v>
+      </c>
+      <c r="B25" s="1">
+        <v>3.8400000000000001E-4</v>
+      </c>
+      <c r="C25" s="1">
+        <v>3.8400000000000001E-4</v>
+      </c>
+      <c r="D25" t="s">
+        <v>97</v>
+      </c>
+      <c r="E25" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A26" t="s">
+        <v>85</v>
+      </c>
+      <c r="B26" s="1">
+        <v>2.0699999999999999E-4</v>
+      </c>
+      <c r="C26" s="1">
+        <v>2.0699999999999999E-4</v>
+      </c>
+      <c r="D26" t="s">
+        <v>86</v>
+      </c>
+      <c r="E26" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A27" t="s">
+        <v>98</v>
+      </c>
+      <c r="B27" s="1">
+        <v>1.92E-4</v>
+      </c>
+      <c r="C27" s="1">
+        <v>1.92E-4</v>
+      </c>
+      <c r="D27" t="s">
+        <v>99</v>
+      </c>
+      <c r="E27" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A28" t="s">
+        <v>169</v>
+      </c>
+      <c r="B28" s="1">
+        <v>1.37E-4</v>
+      </c>
+      <c r="C28" s="1">
+        <v>1.37E-4</v>
+      </c>
+      <c r="D28" t="s">
+        <v>170</v>
+      </c>
+      <c r="E28" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A29" t="s">
+        <v>115</v>
+      </c>
+      <c r="B29" s="1">
+        <v>8.5599999999999994E-5</v>
+      </c>
+      <c r="C29" s="1">
+        <v>8.5599999999999994E-5</v>
+      </c>
+      <c r="D29" t="s">
+        <v>116</v>
+      </c>
+      <c r="E29" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A30" t="s">
+        <v>117</v>
+      </c>
+      <c r="B30" s="1">
+        <v>7.8100000000000001E-5</v>
+      </c>
+      <c r="C30" s="1">
+        <v>7.8100000000000001E-5</v>
+      </c>
+      <c r="D30" t="s">
+        <v>118</v>
+      </c>
+      <c r="E30" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A31" t="s">
+        <v>70</v>
+      </c>
+      <c r="B31" s="1">
+        <v>7.6500000000000003E-5</v>
+      </c>
+      <c r="C31" s="1">
+        <v>7.6500000000000003E-5</v>
+      </c>
+      <c r="D31" t="s">
+        <v>71</v>
+      </c>
+      <c r="E31" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A32" t="s">
         <v>41</v>
       </c>
-      <c r="B17" s="1">
+      <c r="B32" s="1">
         <v>6.2799999999999995E-5</v>
       </c>
-      <c r="C17" s="1">
+      <c r="C32" s="1">
         <v>6.2799999999999995E-5</v>
       </c>
-      <c r="D17" t="s">
+      <c r="D32" t="s">
         <v>42</v>
       </c>
-      <c r="E17" t="s">
+      <c r="E32" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>50</v>
-      </c>
-      <c r="B18" s="1">
-        <v>3.2499999999999997E-5</v>
-      </c>
-      <c r="C18" s="1">
-        <v>3.2499999999999997E-5</v>
-      </c>
-      <c r="D18" t="s">
-        <v>51</v>
-      </c>
-      <c r="E18" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>44</v>
-      </c>
-      <c r="B19" s="1">
-        <v>2.8200000000000001E-5</v>
-      </c>
-      <c r="C19" s="1">
-        <v>1.4800000000000001E-5</v>
-      </c>
-      <c r="D19" t="s">
-        <v>45</v>
-      </c>
-      <c r="E19" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>47</v>
-      </c>
-      <c r="B20" s="1">
-        <v>1.34E-5</v>
-      </c>
-      <c r="C20" s="1">
-        <v>1.34E-5</v>
-      </c>
-      <c r="D20" t="s">
-        <v>48</v>
-      </c>
-      <c r="E20" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>53</v>
-      </c>
-      <c r="B21" s="1">
-        <v>2.6100000000000001E-5</v>
-      </c>
-      <c r="C21" s="1">
-        <v>2.6100000000000001E-5</v>
-      </c>
-      <c r="D21" t="s">
-        <v>54</v>
-      </c>
-      <c r="E21" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>59</v>
-      </c>
-      <c r="B22" s="1">
-        <v>5.4500000000000003E-6</v>
-      </c>
-      <c r="C22" s="1">
-        <v>5.4500000000000003E-6</v>
-      </c>
-      <c r="D22" t="s">
-        <v>60</v>
-      </c>
-      <c r="E22" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>56</v>
-      </c>
-      <c r="B23" s="1">
-        <v>4.0899999999999998E-6</v>
-      </c>
-      <c r="C23" s="1">
-        <v>4.0899999999999998E-6</v>
-      </c>
-      <c r="D23" t="s">
-        <v>57</v>
-      </c>
-      <c r="E23" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>61</v>
-      </c>
-      <c r="B24" s="1">
-        <v>8.6799999999999996E-4</v>
-      </c>
-      <c r="C24" s="1">
-        <v>5.2599999999999996E-6</v>
-      </c>
-      <c r="D24" t="s">
-        <v>62</v>
-      </c>
-      <c r="E24" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>64</v>
-      </c>
-      <c r="B25" s="1">
-        <v>7.3899999999999997E-4</v>
-      </c>
-      <c r="C25" s="1">
-        <v>7.3899999999999997E-4</v>
-      </c>
-      <c r="D25" t="s">
-        <v>65</v>
-      </c>
-      <c r="E25" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>70</v>
-      </c>
-      <c r="B26" s="1">
-        <v>7.6500000000000003E-5</v>
-      </c>
-      <c r="C26" s="1">
-        <v>7.6500000000000003E-5</v>
-      </c>
-      <c r="D26" t="s">
-        <v>71</v>
-      </c>
-      <c r="E26" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>67</v>
-      </c>
-      <c r="B27" s="1">
-        <v>3.1900000000000003E-5</v>
-      </c>
-      <c r="C27" s="1">
-        <v>3.1900000000000003E-5</v>
-      </c>
-      <c r="D27" t="s">
-        <v>68</v>
-      </c>
-      <c r="E27" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>79</v>
-      </c>
-      <c r="B28" s="1">
-        <v>9.0000000000000002E-6</v>
-      </c>
-      <c r="C28" s="1">
-        <v>9.0000000000000002E-6</v>
-      </c>
-      <c r="D28" t="s">
-        <v>80</v>
-      </c>
-      <c r="E28" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>73</v>
-      </c>
-      <c r="B29" s="1">
-        <v>4.7199999999999997E-6</v>
-      </c>
-      <c r="C29" s="1">
-        <v>4.7199999999999997E-6</v>
-      </c>
-      <c r="D29" t="s">
-        <v>74</v>
-      </c>
-      <c r="E29" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>76</v>
-      </c>
-      <c r="B30" s="1">
-        <v>2.3800000000000001E-6</v>
-      </c>
-      <c r="C30" s="1">
-        <v>2.3800000000000001E-6</v>
-      </c>
-      <c r="D30" t="s">
-        <v>77</v>
-      </c>
-      <c r="E30" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>87</v>
-      </c>
-      <c r="B31" s="1">
-        <v>6.5700000000000003E-4</v>
-      </c>
-      <c r="C31" s="1">
-        <v>1.02E-4</v>
-      </c>
-      <c r="D31" t="s">
-        <v>88</v>
-      </c>
-      <c r="E31" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
-        <v>90</v>
-      </c>
-      <c r="B32" s="1">
-        <v>5.1099999999999995E-4</v>
-      </c>
-      <c r="C32" s="1">
-        <v>5.1099999999999995E-4</v>
-      </c>
-      <c r="D32" t="s">
-        <v>91</v>
-      </c>
-      <c r="E32" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>93</v>
       </c>
@@ -7001,296 +7010,296 @@
         <v>95</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
-        <v>82</v>
+        <v>101</v>
       </c>
       <c r="B34" s="1">
-        <v>3.9300000000000001E-4</v>
+        <v>4.2799999999999997E-5</v>
       </c>
       <c r="C34" s="1">
-        <v>3.9300000000000001E-4</v>
+        <v>4.2799999999999997E-5</v>
       </c>
       <c r="D34" t="s">
-        <v>83</v>
+        <v>102</v>
       </c>
       <c r="E34" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="B35" s="1">
-        <v>3.8400000000000001E-4</v>
+        <v>3.9799999999999998E-5</v>
       </c>
       <c r="C35" s="1">
-        <v>3.8400000000000001E-4</v>
+        <v>3.9799999999999998E-5</v>
       </c>
       <c r="D35" t="s">
-        <v>97</v>
+        <v>106</v>
       </c>
       <c r="E35" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
-        <v>85</v>
+        <v>103</v>
       </c>
       <c r="B36" s="1">
-        <v>2.0699999999999999E-4</v>
+        <v>3.96E-5</v>
       </c>
       <c r="C36" s="1">
-        <v>2.0699999999999999E-4</v>
+        <v>3.96E-5</v>
       </c>
       <c r="D36" t="s">
-        <v>86</v>
+        <v>104</v>
       </c>
       <c r="E36" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
-        <v>98</v>
+        <v>50</v>
       </c>
       <c r="B37" s="1">
-        <v>1.92E-4</v>
+        <v>3.2499999999999997E-5</v>
       </c>
       <c r="C37" s="1">
-        <v>1.92E-4</v>
+        <v>3.2499999999999997E-5</v>
       </c>
       <c r="D37" t="s">
-        <v>99</v>
+        <v>51</v>
       </c>
       <c r="E37" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
-        <v>115</v>
+        <v>67</v>
       </c>
       <c r="B38" s="1">
-        <v>8.5599999999999994E-5</v>
+        <v>3.1900000000000003E-5</v>
       </c>
       <c r="C38" s="1">
-        <v>8.5599999999999994E-5</v>
+        <v>3.1900000000000003E-5</v>
       </c>
       <c r="D38" t="s">
-        <v>116</v>
+        <v>68</v>
       </c>
       <c r="E38" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="B39" s="1">
-        <v>7.8100000000000001E-5</v>
+        <v>3.1199999999999999E-5</v>
       </c>
       <c r="C39" s="1">
-        <v>7.8100000000000001E-5</v>
+        <v>3.1199999999999999E-5</v>
       </c>
       <c r="D39" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="E39" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
-        <v>101</v>
+        <v>113</v>
       </c>
       <c r="B40" s="1">
-        <v>4.2799999999999997E-5</v>
+        <v>2.9899999999999998E-5</v>
       </c>
       <c r="C40" s="1">
-        <v>4.2799999999999997E-5</v>
+        <v>2.9899999999999998E-5</v>
       </c>
       <c r="D40" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="E40" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
-        <v>105</v>
+        <v>148</v>
       </c>
       <c r="B41" s="1">
-        <v>3.9799999999999998E-5</v>
+        <v>2.9499999999999999E-5</v>
       </c>
       <c r="C41" s="1">
-        <v>3.9799999999999998E-5</v>
+        <v>2.9499999999999999E-5</v>
       </c>
       <c r="D41" t="s">
-        <v>106</v>
+        <v>149</v>
       </c>
       <c r="E41" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
-        <v>103</v>
+        <v>44</v>
       </c>
       <c r="B42" s="1">
-        <v>3.96E-5</v>
+        <v>2.8200000000000001E-5</v>
       </c>
       <c r="C42" s="1">
-        <v>3.96E-5</v>
+        <v>1.4800000000000001E-5</v>
       </c>
       <c r="D42" t="s">
-        <v>104</v>
+        <v>45</v>
       </c>
       <c r="E42" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
-        <v>111</v>
+        <v>172</v>
       </c>
       <c r="B43" s="1">
-        <v>3.1199999999999999E-5</v>
+        <v>2.62E-5</v>
       </c>
       <c r="C43" s="1">
-        <v>3.1199999999999999E-5</v>
+        <v>2.62E-5</v>
       </c>
       <c r="D43" t="s">
-        <v>112</v>
+        <v>173</v>
       </c>
       <c r="E43" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
-        <v>113</v>
+        <v>53</v>
       </c>
       <c r="B44" s="1">
-        <v>2.9899999999999998E-5</v>
+        <v>2.6100000000000001E-5</v>
       </c>
       <c r="C44" s="1">
-        <v>2.9899999999999998E-5</v>
+        <v>2.6100000000000001E-5</v>
       </c>
       <c r="D44" t="s">
-        <v>114</v>
+        <v>54</v>
       </c>
       <c r="E44" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="B45" s="1">
-        <v>2.9499999999999999E-5</v>
+        <v>2.55E-5</v>
       </c>
       <c r="C45" s="1">
-        <v>2.9499999999999999E-5</v>
+        <v>2.55E-5</v>
       </c>
       <c r="D45" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="E45" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
-        <v>150</v>
+        <v>109</v>
       </c>
       <c r="B46" s="1">
-        <v>2.55E-5</v>
+        <v>2.4600000000000002E-5</v>
       </c>
       <c r="C46" s="1">
-        <v>2.55E-5</v>
+        <v>2.4600000000000002E-5</v>
       </c>
       <c r="D46" t="s">
-        <v>151</v>
+        <v>110</v>
       </c>
       <c r="E46" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="B47" s="1">
-        <v>2.4600000000000002E-5</v>
+        <v>2.4199999999999999E-5</v>
       </c>
       <c r="C47" s="1">
-        <v>2.4600000000000002E-5</v>
+        <v>2.4199999999999999E-5</v>
       </c>
       <c r="D47" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="E47" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
-        <v>107</v>
+        <v>126</v>
       </c>
       <c r="B48" s="1">
-        <v>2.4199999999999999E-5</v>
+        <v>2.34E-5</v>
       </c>
       <c r="C48" s="1">
-        <v>2.4199999999999999E-5</v>
+        <v>2.34E-5</v>
       </c>
       <c r="D48" t="s">
-        <v>108</v>
+        <v>127</v>
       </c>
       <c r="E48" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="B49" s="1">
-        <v>2.34E-5</v>
+        <v>2.0599999999999999E-5</v>
       </c>
       <c r="C49" s="1">
-        <v>2.34E-5</v>
+        <v>2.0599999999999999E-5</v>
       </c>
       <c r="D49" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="E49" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
-        <v>121</v>
+        <v>38</v>
       </c>
       <c r="B50" s="1">
-        <v>2.0599999999999999E-5</v>
+        <v>1.7799999999999999E-5</v>
       </c>
       <c r="C50" s="1">
-        <v>2.0599999999999999E-5</v>
+        <v>1.7799999999999999E-5</v>
       </c>
       <c r="D50" t="s">
-        <v>122</v>
+        <v>39</v>
       </c>
       <c r="E50" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>119</v>
       </c>
@@ -7307,381 +7316,381 @@
         <v>84</v>
       </c>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
+        <v>47</v>
+      </c>
+      <c r="B52" s="1">
+        <v>1.34E-5</v>
+      </c>
+      <c r="C52" s="1">
+        <v>1.34E-5</v>
+      </c>
+      <c r="D52" t="s">
+        <v>48</v>
+      </c>
+      <c r="E52" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A53" t="s">
         <v>128</v>
       </c>
-      <c r="B52" s="1">
+      <c r="B53" s="1">
         <v>1.27E-5</v>
       </c>
-      <c r="C52" s="1">
+      <c r="C53" s="1">
         <v>1.27E-5</v>
       </c>
-      <c r="D52" t="s">
+      <c r="D53" t="s">
         <v>129</v>
       </c>
-      <c r="E52" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A53" t="s">
+      <c r="E53" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A54" t="s">
         <v>132</v>
       </c>
-      <c r="B53" s="1">
+      <c r="B54" s="1">
         <v>1.2300000000000001E-5</v>
       </c>
-      <c r="C53" s="1">
+      <c r="C54" s="1">
         <v>1.2300000000000001E-5</v>
       </c>
-      <c r="D53" t="s">
+      <c r="D54" t="s">
         <v>133</v>
       </c>
-      <c r="E53" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A54" t="s">
+      <c r="E54" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A55" t="s">
         <v>130</v>
       </c>
-      <c r="B54" s="1">
+      <c r="B55" s="1">
         <v>1.1199999999999999E-5</v>
       </c>
-      <c r="C54" s="1">
+      <c r="C55" s="1">
         <v>1.1199999999999999E-5</v>
       </c>
-      <c r="D54" t="s">
+      <c r="D55" t="s">
         <v>131</v>
       </c>
-      <c r="E54" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A55" t="s">
+      <c r="E55" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A56" t="s">
         <v>154</v>
       </c>
-      <c r="B55" s="1">
+      <c r="B56" s="1">
         <v>9.2199999999999998E-6</v>
       </c>
-      <c r="C55" s="1">
+      <c r="C56" s="1">
         <v>9.2199999999999998E-6</v>
       </c>
-      <c r="D55" t="s">
+      <c r="D56" t="s">
         <v>155</v>
-      </c>
-      <c r="E55" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A56" t="s">
-        <v>134</v>
-      </c>
-      <c r="B56" s="1">
-        <v>6.3400000000000003E-6</v>
-      </c>
-      <c r="C56" s="1">
-        <v>6.3400000000000003E-6</v>
-      </c>
-      <c r="D56" t="s">
-        <v>135</v>
       </c>
       <c r="E56" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
-        <v>136</v>
+        <v>79</v>
       </c>
       <c r="B57" s="1">
-        <v>5.8900000000000004E-6</v>
+        <v>9.0000000000000002E-6</v>
       </c>
       <c r="C57" s="1">
-        <v>5.8900000000000004E-6</v>
+        <v>9.0000000000000002E-6</v>
       </c>
       <c r="D57" t="s">
-        <v>137</v>
+        <v>80</v>
       </c>
       <c r="E57" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="B58" s="1">
-        <v>4.2400000000000001E-6</v>
+        <v>6.3400000000000003E-6</v>
       </c>
       <c r="C58" s="1">
-        <v>4.2400000000000001E-6</v>
+        <v>6.3400000000000003E-6</v>
       </c>
       <c r="D58" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="E58" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
-        <v>123</v>
+        <v>136</v>
       </c>
       <c r="B59" s="1">
-        <v>3.4999999999999999E-6</v>
+        <v>5.8900000000000004E-6</v>
       </c>
       <c r="C59" s="1">
-        <v>3.4999999999999999E-6</v>
+        <v>5.8900000000000004E-6</v>
       </c>
       <c r="D59" t="s">
-        <v>124</v>
+        <v>137</v>
       </c>
       <c r="E59" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
+        <v>59</v>
+      </c>
+      <c r="B60" s="1">
+        <v>5.4500000000000003E-6</v>
+      </c>
+      <c r="C60" s="1">
+        <v>5.4500000000000003E-6</v>
+      </c>
+      <c r="D60" t="s">
+        <v>60</v>
+      </c>
+      <c r="E60" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A61" t="s">
+        <v>73</v>
+      </c>
+      <c r="B61" s="1">
+        <v>4.7199999999999997E-6</v>
+      </c>
+      <c r="C61" s="1">
+        <v>4.7199999999999997E-6</v>
+      </c>
+      <c r="D61" t="s">
+        <v>74</v>
+      </c>
+      <c r="E61" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A62" t="s">
+        <v>38</v>
+      </c>
+      <c r="B62" s="1">
+        <v>4.6199999999999998E-6</v>
+      </c>
+      <c r="C62" s="1">
+        <v>4.6199999999999998E-6</v>
+      </c>
+      <c r="D62" t="s">
+        <v>168</v>
+      </c>
+      <c r="E62" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A63" t="s">
+        <v>138</v>
+      </c>
+      <c r="B63" s="1">
+        <v>4.2400000000000001E-6</v>
+      </c>
+      <c r="C63" s="1">
+        <v>4.2400000000000001E-6</v>
+      </c>
+      <c r="D63" t="s">
+        <v>139</v>
+      </c>
+      <c r="E63" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A64" t="s">
+        <v>56</v>
+      </c>
+      <c r="B64" s="1">
+        <v>4.0899999999999998E-6</v>
+      </c>
+      <c r="C64" s="1">
+        <v>4.0899999999999998E-6</v>
+      </c>
+      <c r="D64" t="s">
+        <v>57</v>
+      </c>
+      <c r="E64" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A65" t="s">
+        <v>123</v>
+      </c>
+      <c r="B65" s="1">
+        <v>3.4999999999999999E-6</v>
+      </c>
+      <c r="C65" s="1">
+        <v>3.4999999999999999E-6</v>
+      </c>
+      <c r="D65" t="s">
+        <v>124</v>
+      </c>
+      <c r="E65" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A66" t="s">
+        <v>76</v>
+      </c>
+      <c r="B66" s="1">
+        <v>2.3800000000000001E-6</v>
+      </c>
+      <c r="C66" s="1">
+        <v>2.3800000000000001E-6</v>
+      </c>
+      <c r="D66" t="s">
+        <v>77</v>
+      </c>
+      <c r="E66" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A67" t="s">
         <v>140</v>
       </c>
-      <c r="B60" s="1">
+      <c r="B67" s="1">
         <v>1.2899999999999999E-6</v>
       </c>
-      <c r="C60" s="1">
+      <c r="C67" s="1">
         <v>1.2899999999999999E-6</v>
       </c>
-      <c r="D60" t="s">
+      <c r="D67" t="s">
         <v>141</v>
       </c>
-      <c r="E60" t="s">
+      <c r="E67" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A61" t="s">
+    <row r="68" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A68" t="s">
         <v>142</v>
       </c>
-      <c r="B61" s="1">
+      <c r="B68" s="1">
         <v>7.7100000000000001E-7</v>
       </c>
-      <c r="C61" s="1">
+      <c r="C68" s="1">
         <v>7.7100000000000001E-7</v>
       </c>
-      <c r="D61" t="s">
+      <c r="D68" t="s">
         <v>143</v>
       </c>
-      <c r="E61" t="s">
+      <c r="E68" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A62" t="s">
+    <row r="69" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A69" t="s">
+        <v>175</v>
+      </c>
+      <c r="B69" s="1">
+        <v>5.5700000000000002E-7</v>
+      </c>
+      <c r="C69" s="1">
+        <v>5.5700000000000002E-7</v>
+      </c>
+      <c r="D69" t="s">
+        <v>176</v>
+      </c>
+      <c r="E69" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A70" t="s">
         <v>146</v>
       </c>
-      <c r="B62" s="1">
+      <c r="B70" s="1">
         <v>5.2600000000000002E-7</v>
       </c>
-      <c r="C62" s="1">
+      <c r="C70" s="1">
         <v>5.2600000000000002E-7</v>
       </c>
-      <c r="D62" t="s">
+      <c r="D70" t="s">
         <v>147</v>
       </c>
-      <c r="E62" t="s">
+      <c r="E70" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A63" t="s">
+    <row r="71" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A71" t="s">
         <v>144</v>
       </c>
-      <c r="B63" s="1">
+      <c r="B71" s="1">
         <v>4.3500000000000002E-7</v>
       </c>
-      <c r="C63" s="1">
+      <c r="C71" s="1">
         <v>4.3500000000000002E-7</v>
       </c>
-      <c r="D63" t="s">
+      <c r="D71" t="s">
         <v>145</v>
       </c>
-      <c r="E63" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A64" t="s">
+      <c r="E71" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A72" t="s">
         <v>152</v>
       </c>
-      <c r="B64" s="1">
+      <c r="B72" s="1">
         <v>3.2599999999999998E-7</v>
       </c>
-      <c r="C64" s="1">
+      <c r="C72" s="1">
         <v>3.2599999999999998E-7</v>
       </c>
-      <c r="D64" t="s">
+      <c r="D72" t="s">
         <v>153</v>
       </c>
-      <c r="E64" t="s">
+      <c r="E72" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A65" t="s">
-        <v>156</v>
-      </c>
-      <c r="B65" s="1">
-        <v>7.0699999999999995E-4</v>
-      </c>
-      <c r="C65">
-        <v>0</v>
-      </c>
-      <c r="D65" t="s">
-        <v>157</v>
-      </c>
-      <c r="E65" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A66" t="s">
-        <v>159</v>
-      </c>
-      <c r="B66" s="1">
-        <v>7.0699999999999995E-4</v>
-      </c>
-      <c r="C66">
-        <v>0</v>
-      </c>
-      <c r="D66" t="s">
-        <v>160</v>
-      </c>
-      <c r="E66" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A67" t="s">
-        <v>32</v>
-      </c>
-      <c r="B67" s="1">
-        <v>7.0699999999999995E-4</v>
-      </c>
-      <c r="C67">
-        <v>0</v>
-      </c>
-      <c r="D67" t="s">
-        <v>161</v>
-      </c>
-      <c r="E67" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A68" t="s">
-        <v>35</v>
-      </c>
-      <c r="B68" s="1">
-        <v>7.0699999999999995E-4</v>
-      </c>
-      <c r="C68" s="1">
-        <v>7.0200000000000004E-4</v>
-      </c>
-      <c r="D68" t="s">
-        <v>163</v>
-      </c>
-      <c r="E68" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A69" t="s">
-        <v>38</v>
-      </c>
-      <c r="B69" s="1">
-        <v>4.6199999999999998E-6</v>
-      </c>
-      <c r="C69" s="1">
-        <v>4.6199999999999998E-6</v>
-      </c>
-      <c r="D69" t="s">
-        <v>168</v>
-      </c>
-      <c r="E69" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A70" t="s">
+    <row r="73" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A73" t="s">
         <v>165</v>
       </c>
-      <c r="B70" s="1">
+      <c r="B73" s="1">
         <v>1.37E-7</v>
       </c>
-      <c r="C70" s="1">
+      <c r="C73" s="1">
         <v>1.37E-7</v>
       </c>
-      <c r="D70" t="s">
+      <c r="D73" t="s">
         <v>166</v>
       </c>
-      <c r="E70" t="s">
+      <c r="E73" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A71" t="s">
-        <v>169</v>
-      </c>
-      <c r="B71" s="1">
-        <v>1.37E-4</v>
-      </c>
-      <c r="C71" s="1">
-        <v>1.37E-4</v>
-      </c>
-      <c r="D71" t="s">
-        <v>170</v>
-      </c>
-      <c r="E71" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A72" t="s">
-        <v>172</v>
-      </c>
-      <c r="B72" s="1">
-        <v>2.62E-5</v>
-      </c>
-      <c r="C72" s="1">
-        <v>2.62E-5</v>
-      </c>
-      <c r="D72" t="s">
-        <v>173</v>
-      </c>
-      <c r="E72" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A73" t="s">
-        <v>175</v>
-      </c>
-      <c r="B73" s="1">
-        <v>5.5700000000000002E-7</v>
-      </c>
-      <c r="C73" s="1">
-        <v>5.5700000000000002E-7</v>
-      </c>
-      <c r="D73" t="s">
-        <v>176</v>
-      </c>
-      <c r="E73" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
         <v>178</v>
       </c>
@@ -7698,7 +7707,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
         <v>181</v>
       </c>
@@ -7715,7 +7724,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
         <v>184</v>
       </c>
